--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -40539,7 +40539,7 @@
         <v/>
       </c>
       <c r="G423" t="str">
-        <v>Flight-inferred country Italy from VY6342→BA591 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-08 07:04:52 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 07:04:52 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST</v>
+        <v>Flight-inferred country Italy from VY6342→BA591 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-08 07:04:52 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 07:04:52 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-08 11:33:30 BST</v>
       </c>
       <c r="H423" t="str">
         <v>45.8409843</v>
@@ -40717,10 +40717,10 @@
         <v>Saturday</v>
       </c>
       <c r="C425" t="str">
-        <v/>
+        <v>Woodlands Road</v>
       </c>
       <c r="D425" t="str">
-        <v>London</v>
+        <v>South Oxfordshire</v>
       </c>
       <c r="E425" t="str">
         <v>UK</v>
@@ -40732,10 +40732,10 @@
         <v/>
       </c>
       <c r="H425" t="str">
-        <v/>
+        <v>51.5210034</v>
       </c>
       <c r="I425" t="str">
-        <v/>
+        <v>-0.904684</v>
       </c>
       <c r="J425" t="str">
         <v/>
@@ -40765,16 +40765,16 @@
         <v>2026-10-10 07:17:08 BST</v>
       </c>
       <c r="S425" t="str">
-        <v/>
+        <v>South Oxfordshire</v>
       </c>
       <c r="T425" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="U425" t="str">
-        <v/>
+        <v>51.52100, -0.90468</v>
       </c>
       <c r="V425" t="str">
-        <v/>
+        <v>2026-10-11 08:36:29 BST</v>
       </c>
       <c r="W425" t="str">
         <v/>
@@ -40789,7 +40789,7 @@
         <v/>
       </c>
       <c r="AA425" t="str">
-        <v>Flight says UK; GPS brackets differ (ev=Italy, am=-) — kept flight country, please confirm</v>
+        <v>Flight says UK; GPS brackets differ (ev=Italy, am=UK) — kept flight country, please confirm</v>
       </c>
       <c r="AB425" t="str">
         <v>calendar: Flight BA591: MXP - LHR, departs 08:10</v>
@@ -40848,16 +40848,16 @@
         <v>Booking</v>
       </c>
       <c r="O426" t="str">
-        <v/>
+        <v>South Oxfordshire</v>
       </c>
       <c r="P426" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q426" t="str">
-        <v/>
+        <v>51.52100, -0.90468</v>
       </c>
       <c r="R426" t="str">
-        <v/>
+        <v>2026-10-11 08:36:30 BST</v>
       </c>
       <c r="S426" t="str">
         <v/>
@@ -40875,10 +40875,10 @@
         <v/>
       </c>
       <c r="X426" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y426" t="str">
-        <v/>
+        <v>08:36 UK South Oxfordshire, UK</v>
       </c>
       <c r="Z426" t="str">
         <v/>
@@ -42370,7 +42370,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-10</v>
+        <v>2026-10-11</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -40848,40 +40848,40 @@
         <v>Booking</v>
       </c>
       <c r="O426" t="str">
-        <v>South Oxfordshire</v>
+        <v>Oxford</v>
       </c>
       <c r="P426" t="str">
         <v>UK</v>
       </c>
       <c r="Q426" t="str">
-        <v>51.52100, -0.90468</v>
+        <v>51.73306, -1.23849</v>
       </c>
       <c r="R426" t="str">
-        <v>2026-10-11 08:36:30 BST</v>
+        <v>2026-10-11 18:38:39 BST</v>
       </c>
       <c r="S426" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="T426" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="U426" t="str">
-        <v/>
+        <v>51.73296, -1.23724</v>
       </c>
       <c r="V426" t="str">
-        <v/>
+        <v>2026-10-12 08:07:54 BST</v>
       </c>
       <c r="W426" t="str">
         <v/>
       </c>
       <c r="X426" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y426" t="str">
-        <v>08:36 UK South Oxfordshire, UK</v>
+        <v>08:36 UK South Oxfordshire, UK | 15:22 UK Oxford, UK | 18:38 UK Oxford, UK</v>
       </c>
       <c r="Z426" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA426" t="str">
         <v/>
@@ -40907,52 +40907,52 @@
         <v>Monday</v>
       </c>
       <c r="C427" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D427" t="str">
-        <v>London</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E427" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F427" t="str">
         <v>BA590</v>
       </c>
       <c r="G427" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-12 08:07:54 BST | Inferred from evening bracket at known location: Oxford 2026-10-12 08:07:54 BST</v>
       </c>
       <c r="H427" t="str">
-        <v/>
+        <v>51.7329593</v>
       </c>
       <c r="I427" t="str">
-        <v/>
+        <v>-1.2372358</v>
       </c>
       <c r="J427" t="str">
-        <v/>
+        <v>2026-10-12 08:07:54 BST</v>
       </c>
       <c r="K427" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L427" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="M427" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="N427" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O427" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="P427" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q427" t="str">
-        <v/>
+        <v>51.73296, -1.23724</v>
       </c>
       <c r="R427" t="str">
-        <v/>
+        <v>2026-10-12 08:07:54 BST</v>
       </c>
       <c r="S427" t="str">
         <v/>
@@ -40967,13 +40967,13 @@
         <v/>
       </c>
       <c r="W427" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X427" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y427" t="str">
-        <v/>
+        <v>08:07 UK Oxford, UK</v>
       </c>
       <c r="Z427" t="str">
         <v/>
@@ -40985,13 +40985,13 @@
         <v>calendar: Flight BA590: LHR - MXP, departs 20:40 | calendar: Cangruppo Options</v>
       </c>
       <c r="AC427" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD427" t="str">
         <v>Yes</v>
       </c>
       <c r="AE427" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
     </row>
     <row r="428">
@@ -42162,7 +42162,7 @@
         <v>UK</v>
       </c>
       <c r="B2">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3">
@@ -42170,7 +42170,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -42314,7 +42314,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
@@ -42322,7 +42322,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="24">
@@ -42330,7 +42330,7 @@
         <v>UK work days (max 30)</v>
       </c>
       <c r="B24">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -42354,7 +42354,7 @@
         <v>Total work days</v>
       </c>
       <c r="B27">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="28">
@@ -42370,7 +42370,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-11</v>
+        <v>2026-10-12</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -40812,10 +40812,10 @@
         <v>Sunday</v>
       </c>
       <c r="C426" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="D426" t="str">
-        <v>London</v>
+        <v>Oxford</v>
       </c>
       <c r="E426" t="str">
         <v>UK</v>
@@ -40824,19 +40824,19 @@
         <v/>
       </c>
       <c r="G426" t="str">
-        <v>Flight-inferred country UK from BA590 direction (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA590 direction (UK midnight rule). | Retracted stale flight-inference (flight-inference: BA590) — supporting flights no longer found. | Inferred from GPS brackets: evening=Oxford 2026-10-11 18:38:39 BST, morning=Oxford 2026-10-12 08:07:54 BST</v>
       </c>
       <c r="H426" t="str">
-        <v/>
+        <v>51.7330557</v>
       </c>
       <c r="I426" t="str">
-        <v/>
+        <v>-1.2384911</v>
       </c>
       <c r="J426" t="str">
-        <v/>
+        <v>2026-10-11 18:38:39 BST</v>
       </c>
       <c r="K426" t="str">
-        <v/>
+        <v>bracket-inference</v>
       </c>
       <c r="L426" t="str">
         <v/>
@@ -40845,7 +40845,7 @@
         <v/>
       </c>
       <c r="N426" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O426" t="str">
         <v>Oxford</v>
@@ -40872,7 +40872,7 @@
         <v>2026-10-12 08:07:54 BST</v>
       </c>
       <c r="W426" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X426" t="str">
         <v>3</v>
@@ -40887,13 +40887,13 @@
         <v/>
       </c>
       <c r="AB426" t="str">
-        <v>flight-inference: BA590</v>
+        <v/>
       </c>
       <c r="AC426" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD426" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE426" t="str">
         <v/>
@@ -40943,37 +40943,37 @@
         <v>Bracket GPS</v>
       </c>
       <c r="O427" t="str">
-        <v>Oxford</v>
+        <v>Ferno</v>
       </c>
       <c r="P427" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="Q427" t="str">
-        <v>51.73296, -1.23724</v>
+        <v>45.62771, 8.71474</v>
       </c>
       <c r="R427" t="str">
-        <v>2026-10-12 08:07:54 BST</v>
+        <v>2026-10-12 22:58:09 BST</v>
       </c>
       <c r="S427" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="T427" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="U427" t="str">
-        <v/>
+        <v>45.84364, 9.06664</v>
       </c>
       <c r="V427" t="str">
-        <v/>
+        <v>2026-10-13 00:56:31 BST</v>
       </c>
       <c r="W427" t="str">
         <v>Yes</v>
       </c>
       <c r="X427" t="str">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y427" t="str">
-        <v>08:07 UK Oxford, UK</v>
+        <v>08:07 UK Oxford, UK | 14:59 UK Spencers Wood, UK | 22:58 UK/23:58 Europe/Rome Ferno, Italy</v>
       </c>
       <c r="Z427" t="str">
         <v/>
@@ -41005,16 +41005,16 @@
         <v/>
       </c>
       <c r="D428" t="str">
-        <v>London</v>
+        <v>Milan</v>
       </c>
       <c r="E428" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F428" t="str">
         <v/>
       </c>
       <c r="G428" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country Italy from LO320 direction (UK midnight rule).</v>
       </c>
       <c r="H428" t="str">
         <v/>
@@ -41038,16 +41038,16 @@
         <v>Booking</v>
       </c>
       <c r="O428" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P428" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q428" t="str">
-        <v/>
+        <v>45.84364, 9.06664</v>
       </c>
       <c r="R428" t="str">
-        <v/>
+        <v>2026-10-13 00:56:31 BST</v>
       </c>
       <c r="S428" t="str">
         <v/>
@@ -41065,10 +41065,10 @@
         <v/>
       </c>
       <c r="X428" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y428" t="str">
-        <v/>
+        <v>00:56 UK/01:56 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z428" t="str">
         <v/>
@@ -41106,7 +41106,7 @@
         <v>Poland</v>
       </c>
       <c r="F429" t="str">
-        <v/>
+        <v>LO320</v>
       </c>
       <c r="G429" t="str">
         <v/>
@@ -41172,7 +41172,7 @@
         <v/>
       </c>
       <c r="AB429" t="str">
-        <v>calendar: ALSO speaking event</v>
+        <v>calendar: ALSO speaking event | calendar: Flight LO 320: MXP - WAW, departs 19:40 | ALSO speaking event</v>
       </c>
       <c r="AC429" t="str">
         <v/>
@@ -41290,13 +41290,13 @@
         <v>Poland</v>
       </c>
       <c r="D431" t="str">
-        <v>Poland</v>
+        <v>London</v>
       </c>
       <c r="E431" t="str">
-        <v>Poland</v>
+        <v>UK</v>
       </c>
       <c r="F431" t="str">
-        <v/>
+        <v>BA847</v>
       </c>
       <c r="G431" t="str">
         <v/>
@@ -41362,7 +41362,7 @@
         <v/>
       </c>
       <c r="AB431" t="str">
-        <v>calendar: ALSO speaking event</v>
+        <v>calendar: ALSO speaking event | calendar: Flight: BA847 - Warsaw to LHR, departs 08:15 AM | ALSO speaking event</v>
       </c>
       <c r="AC431" t="str">
         <v/>
@@ -41480,13 +41480,13 @@
         <v/>
       </c>
       <c r="D433" t="str">
-        <v>London</v>
+        <v>Milan</v>
       </c>
       <c r="E433" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F433" t="str">
-        <v/>
+        <v>BA590</v>
       </c>
       <c r="G433" t="str">
         <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule).</v>
@@ -41552,7 +41552,7 @@
         <v/>
       </c>
       <c r="AB433" t="str">
-        <v>flight-inference: BA591→BA590</v>
+        <v>flight-inference: BA591→BA590 | calendar: Flight BA590: LHR - MXP, departs 20:40</v>
       </c>
       <c r="AC433" t="str">
         <v/>
@@ -41575,16 +41575,16 @@
         <v/>
       </c>
       <c r="D434" t="str">
-        <v>London</v>
+        <v/>
       </c>
       <c r="E434" t="str">
-        <v>UK</v>
+        <v/>
       </c>
       <c r="F434" t="str">
         <v/>
       </c>
       <c r="G434" t="str">
-        <v>Flight-inferred country UK from BA590 direction (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA590 direction (UK midnight rule). | Retracted stale flight-inference (flight-inference: BA590) — supporting flights no longer found.</v>
       </c>
       <c r="H434" t="str">
         <v/>
@@ -41596,7 +41596,7 @@
         <v/>
       </c>
       <c r="K434" t="str">
-        <v/>
+        <v>flight-inference-retracted</v>
       </c>
       <c r="L434" t="str">
         <v/>
@@ -41605,7 +41605,7 @@
         <v/>
       </c>
       <c r="N434" t="str">
-        <v>Booking</v>
+        <v/>
       </c>
       <c r="O434" t="str">
         <v/>
@@ -41647,13 +41647,13 @@
         <v/>
       </c>
       <c r="AB434" t="str">
-        <v>flight-inference: BA590</v>
+        <v/>
       </c>
       <c r="AC434" t="str">
         <v/>
       </c>
       <c r="AD434" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE434" t="str">
         <v/>
@@ -42162,7 +42162,7 @@
         <v>UK</v>
       </c>
       <c r="B2">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="3">
@@ -42170,7 +42170,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4">
@@ -42186,7 +42186,7 @@
         <v>Unrecorded</v>
       </c>
       <c r="B5">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -42266,7 +42266,7 @@
         <v>Poland</v>
       </c>
       <c r="B15">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -42314,7 +42314,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B22">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="23">
@@ -42322,7 +42322,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
@@ -42370,7 +42370,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-12</v>
+        <v>2026-10-13</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -41044,10 +41044,10 @@
         <v>Italy</v>
       </c>
       <c r="Q428" t="str">
-        <v>45.84364, 9.06664</v>
+        <v>45.84597, 9.07996</v>
       </c>
       <c r="R428" t="str">
-        <v>2026-10-13 00:56:31 BST</v>
+        <v>2026-10-13 17:40:39 BST</v>
       </c>
       <c r="S428" t="str">
         <v/>
@@ -41065,13 +41065,13 @@
         <v/>
       </c>
       <c r="X428" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y428" t="str">
-        <v>00:56 UK/01:56 Europe/Rome Cernobbio, Italy</v>
+        <v>00:56 UK/01:56 Europe/Rome Cernobbio, Italy | 17:40 UK/18:40 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z428" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA428" t="str">
         <v/>
@@ -41480,16 +41480,16 @@
         <v/>
       </c>
       <c r="D433" t="str">
-        <v>Milan</v>
+        <v>London</v>
       </c>
       <c r="E433" t="str">
-        <v>Italy</v>
+        <v>UK</v>
       </c>
       <c r="F433" t="str">
         <v>BA590</v>
       </c>
       <c r="G433" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule).</v>
       </c>
       <c r="H433" t="str">
         <v/>
@@ -41552,7 +41552,7 @@
         <v/>
       </c>
       <c r="AB433" t="str">
-        <v>flight-inference: BA591→BA590 | calendar: Flight BA590: LHR - MXP, departs 20:40</v>
+        <v>flight-inference: BA591→BA590 | calendar: Flight BA590: LHR - MXP, departs 20:40 | flight-inference: BA847→BA584</v>
       </c>
       <c r="AC433" t="str">
         <v/>
@@ -41575,16 +41575,16 @@
         <v/>
       </c>
       <c r="D434" t="str">
-        <v/>
+        <v>London</v>
       </c>
       <c r="E434" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F434" t="str">
         <v/>
       </c>
       <c r="G434" t="str">
-        <v>Flight-inferred country UK from BA590 direction (UK midnight rule). | Retracted stale flight-inference (flight-inference: BA590) — supporting flights no longer found.</v>
+        <v>Flight-inferred country UK from BA590 direction (UK midnight rule). | Retracted stale flight-inference (flight-inference: BA590) — supporting flights no longer found. | Flight-inferred country UK from BA584 direction (UK midnight rule).</v>
       </c>
       <c r="H434" t="str">
         <v/>
@@ -41596,7 +41596,7 @@
         <v/>
       </c>
       <c r="K434" t="str">
-        <v>flight-inference-retracted</v>
+        <v/>
       </c>
       <c r="L434" t="str">
         <v/>
@@ -41605,7 +41605,7 @@
         <v/>
       </c>
       <c r="N434" t="str">
-        <v/>
+        <v>Booking</v>
       </c>
       <c r="O434" t="str">
         <v/>
@@ -41647,13 +41647,13 @@
         <v/>
       </c>
       <c r="AB434" t="str">
-        <v/>
+        <v>flight-inference: BA584</v>
       </c>
       <c r="AC434" t="str">
         <v/>
       </c>
       <c r="AD434" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AE434" t="str">
         <v/>
@@ -41676,7 +41676,7 @@
         <v>Italy</v>
       </c>
       <c r="F435" t="str">
-        <v>BA590</v>
+        <v>BA590, BA584</v>
       </c>
       <c r="G435" t="str">
         <v/>
@@ -41742,7 +41742,7 @@
         <v/>
       </c>
       <c r="AB435" t="str">
-        <v>calendar: Flight BA590: LHR - MXP, departs 20:40</v>
+        <v>calendar: Flight BA590: LHR - MXP, departs 20:40 | calendar: Flight BA584: LHR - MXP, departs 10:35</v>
       </c>
       <c r="AC435" t="str">
         <v/>
@@ -42162,7 +42162,7 @@
         <v>UK</v>
       </c>
       <c r="B2">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3">
@@ -42170,7 +42170,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="4">
@@ -42186,7 +42186,7 @@
         <v>Unrecorded</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -42314,7 +42314,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B22">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23">
@@ -42322,7 +42322,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
@@ -42370,7 +42370,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-13</v>
+        <v>2026-10-14</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -41124,46 +41124,46 @@
         <v/>
       </c>
       <c r="L429" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="M429" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="N429" t="str">
         <v>Booking</v>
       </c>
       <c r="O429" t="str">
-        <v/>
+        <v>Warsaw</v>
       </c>
       <c r="P429" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="Q429" t="str">
-        <v/>
+        <v>52.16998, 20.97192</v>
       </c>
       <c r="R429" t="str">
-        <v/>
+        <v>2026-10-14 21:45:07 BST</v>
       </c>
       <c r="S429" t="str">
-        <v/>
+        <v>Warsaw</v>
       </c>
       <c r="T429" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="U429" t="str">
-        <v/>
+        <v>52.24002, 21.02960</v>
       </c>
       <c r="V429" t="str">
-        <v/>
+        <v>2026-10-15 08:19:07 BST</v>
       </c>
       <c r="W429" t="str">
         <v/>
       </c>
       <c r="X429" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="Y429" t="str">
-        <v/>
+        <v>09:32 UK/10:32 Europe/Rome Cernobbio, Italy | 10:55 UK/11:55 Europe/Rome Casnate con Bernate, Italy | 21:45 UK/22:45 Europe/Warsaw Warsaw, Poland</v>
       </c>
       <c r="Z429" t="str">
         <v/>
@@ -41219,25 +41219,25 @@
         <v/>
       </c>
       <c r="L430" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="M430" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="N430" t="str">
         <v>Booking</v>
       </c>
       <c r="O430" t="str">
-        <v/>
+        <v>Warsaw</v>
       </c>
       <c r="P430" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="Q430" t="str">
-        <v/>
+        <v>52.24002, 21.02960</v>
       </c>
       <c r="R430" t="str">
-        <v/>
+        <v>2026-10-15 08:19:07 BST</v>
       </c>
       <c r="S430" t="str">
         <v/>
@@ -41255,10 +41255,10 @@
         <v/>
       </c>
       <c r="X430" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y430" t="str">
-        <v/>
+        <v>08:19 UK/09:19 Europe/Warsaw Warsaw, Poland</v>
       </c>
       <c r="Z430" t="str">
         <v/>
@@ -42346,7 +42346,7 @@
         <v>Rest-of-world work days</v>
       </c>
       <c r="B26">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="27">
@@ -42354,7 +42354,7 @@
         <v>Total work days</v>
       </c>
       <c r="B27">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28">
@@ -42370,7 +42370,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-14</v>
+        <v>2026-10-15</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE439"/>
+  <dimension ref="A1:AE440"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41240,16 +41240,16 @@
         <v>2026-10-15 08:19:07 BST</v>
       </c>
       <c r="S430" t="str">
-        <v/>
+        <v>Warsaw</v>
       </c>
       <c r="T430" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="U430" t="str">
-        <v/>
+        <v>52.24005, 21.02938</v>
       </c>
       <c r="V430" t="str">
-        <v/>
+        <v>2026-10-16 05:39:50 BST</v>
       </c>
       <c r="W430" t="str">
         <v/>
@@ -41261,7 +41261,7 @@
         <v>08:19 UK/09:19 Europe/Warsaw Warsaw, Poland</v>
       </c>
       <c r="Z430" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA430" t="str">
         <v/>
@@ -41287,7 +41287,7 @@
         <v>Friday</v>
       </c>
       <c r="C431" t="str">
-        <v>Poland</v>
+        <v/>
       </c>
       <c r="D431" t="str">
         <v>London</v>
@@ -41323,16 +41323,16 @@
         <v>Booking</v>
       </c>
       <c r="O431" t="str">
-        <v/>
+        <v>Warsaw</v>
       </c>
       <c r="P431" t="str">
-        <v/>
+        <v>Poland</v>
       </c>
       <c r="Q431" t="str">
-        <v/>
+        <v>52.24005, 21.02938</v>
       </c>
       <c r="R431" t="str">
-        <v/>
+        <v>2026-10-16 05:39:50 BST</v>
       </c>
       <c r="S431" t="str">
         <v/>
@@ -41350,16 +41350,16 @@
         <v/>
       </c>
       <c r="X431" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y431" t="str">
-        <v/>
+        <v>05:39 UK/06:39 Europe/Warsaw Warsaw, Poland</v>
       </c>
       <c r="Z431" t="str">
         <v/>
       </c>
       <c r="AA431" t="str">
-        <v/>
+        <v>Flight says UK; GPS brackets differ (ev=Poland, am=-) — kept flight country, please confirm</v>
       </c>
       <c r="AB431" t="str">
         <v>calendar: ALSO speaking event | calendar: Flight: BA847 - Warsaw to LHR, departs 08:15 AM | ALSO speaking event</v>
@@ -41946,22 +41946,22 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>2027-06-04</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B438" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C438" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D438" t="str">
-        <v>Steve Brazier</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E438" t="str">
-        <v/>
+        <v>USA</v>
       </c>
       <c r="F438" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G438" t="str">
         <v/>
@@ -42027,7 +42027,7 @@
         <v/>
       </c>
       <c r="AB438" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC438" t="str">
         <v/>
@@ -42041,10 +42041,10 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="B439" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C439" t="str">
         <v>, Madrid</v>
@@ -42134,9 +42134,104 @@
         <v/>
       </c>
     </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B440" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C440" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D440" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E440" t="str">
+        <v/>
+      </c>
+      <c r="F440" t="str">
+        <v/>
+      </c>
+      <c r="G440" t="str">
+        <v/>
+      </c>
+      <c r="H440" t="str">
+        <v/>
+      </c>
+      <c r="I440" t="str">
+        <v/>
+      </c>
+      <c r="J440" t="str">
+        <v/>
+      </c>
+      <c r="K440" t="str">
+        <v/>
+      </c>
+      <c r="L440" t="str">
+        <v/>
+      </c>
+      <c r="M440" t="str">
+        <v/>
+      </c>
+      <c r="N440" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O440" t="str">
+        <v/>
+      </c>
+      <c r="P440" t="str">
+        <v/>
+      </c>
+      <c r="Q440" t="str">
+        <v/>
+      </c>
+      <c r="R440" t="str">
+        <v/>
+      </c>
+      <c r="S440" t="str">
+        <v/>
+      </c>
+      <c r="T440" t="str">
+        <v/>
+      </c>
+      <c r="U440" t="str">
+        <v/>
+      </c>
+      <c r="V440" t="str">
+        <v/>
+      </c>
+      <c r="W440" t="str">
+        <v/>
+      </c>
+      <c r="X440" t="str">
+        <v/>
+      </c>
+      <c r="Y440" t="str">
+        <v/>
+      </c>
+      <c r="Z440" t="str">
+        <v/>
+      </c>
+      <c r="AA440" t="str">
+        <v/>
+      </c>
+      <c r="AB440" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC440" t="str">
+        <v/>
+      </c>
+      <c r="AD440" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE440" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE439"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE440"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42199,15 +42294,15 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Germany</v>
+        <v>USA</v>
       </c>
       <c r="B7">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>USA</v>
+        <v>Germany</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -42362,7 +42457,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>438</v>
+        <v>439</v>
       </c>
     </row>
     <row r="30">
@@ -42370,7 +42465,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-15</v>
+        <v>2026-10-16</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE440"/>
+  <dimension ref="A1:AE441"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41323,16 +41323,16 @@
         <v>Booking</v>
       </c>
       <c r="O431" t="str">
-        <v>Warsaw</v>
+        <v>Oxford</v>
       </c>
       <c r="P431" t="str">
-        <v>Poland</v>
+        <v>UK</v>
       </c>
       <c r="Q431" t="str">
-        <v>52.24005, 21.02938</v>
+        <v>51.73300, -1.23729</v>
       </c>
       <c r="R431" t="str">
-        <v>2026-10-16 05:39:50 BST</v>
+        <v>2026-10-16 17:07:24 BST</v>
       </c>
       <c r="S431" t="str">
         <v/>
@@ -41350,10 +41350,10 @@
         <v/>
       </c>
       <c r="X431" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y431" t="str">
-        <v>05:39 UK/06:39 Europe/Warsaw Warsaw, Poland</v>
+        <v>05:39 UK/06:39 Europe/Warsaw Warsaw, Poland | 17:07 UK Oxford, UK</v>
       </c>
       <c r="Z431" t="str">
         <v/>
@@ -41756,22 +41756,22 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="B436" t="str">
-        <v>Monday</v>
+        <v>Sunday</v>
       </c>
       <c r="C436" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D436" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>London</v>
       </c>
       <c r="E436" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F436" t="str">
-        <v/>
+        <v>WS001</v>
       </c>
       <c r="G436" t="str">
         <v/>
@@ -41837,7 +41837,7 @@
         <v/>
       </c>
       <c r="AB436" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
       </c>
       <c r="AC436" t="str">
         <v/>
@@ -41851,10 +41851,10 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="B437" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="C437" t="str">
         <v>Fairmont Scottsdale Princess</v>
@@ -41866,7 +41866,7 @@
         <v/>
       </c>
       <c r="F437" t="str">
-        <v/>
+        <v>WS1160</v>
       </c>
       <c r="G437" t="str">
         <v/>
@@ -41932,7 +41932,7 @@
         <v/>
       </c>
       <c r="AB437" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC437" t="str">
         <v/>
@@ -41946,22 +41946,22 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="B438" t="str">
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C438" t="str">
-        <v/>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="D438" t="str">
-        <v>Los Angeles</v>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="E438" t="str">
-        <v>USA</v>
+        <v/>
       </c>
       <c r="F438" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G438" t="str">
         <v/>
@@ -42027,7 +42027,7 @@
         <v/>
       </c>
       <c r="AB438" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC438" t="str">
         <v/>
@@ -42041,22 +42041,22 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>2027-06-04</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B439" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C439" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D439" t="str">
-        <v>Steve Brazier</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E439" t="str">
-        <v/>
+        <v>USA</v>
       </c>
       <c r="F439" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G439" t="str">
         <v/>
@@ -42122,7 +42122,7 @@
         <v/>
       </c>
       <c r="AB439" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC439" t="str">
         <v/>
@@ -42136,10 +42136,10 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="B440" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C440" t="str">
         <v>, Madrid</v>
@@ -42229,9 +42229,104 @@
         <v/>
       </c>
     </row>
+    <row r="441">
+      <c r="A441" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B441" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C441" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D441" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E441" t="str">
+        <v/>
+      </c>
+      <c r="F441" t="str">
+        <v/>
+      </c>
+      <c r="G441" t="str">
+        <v/>
+      </c>
+      <c r="H441" t="str">
+        <v/>
+      </c>
+      <c r="I441" t="str">
+        <v/>
+      </c>
+      <c r="J441" t="str">
+        <v/>
+      </c>
+      <c r="K441" t="str">
+        <v/>
+      </c>
+      <c r="L441" t="str">
+        <v/>
+      </c>
+      <c r="M441" t="str">
+        <v/>
+      </c>
+      <c r="N441" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O441" t="str">
+        <v/>
+      </c>
+      <c r="P441" t="str">
+        <v/>
+      </c>
+      <c r="Q441" t="str">
+        <v/>
+      </c>
+      <c r="R441" t="str">
+        <v/>
+      </c>
+      <c r="S441" t="str">
+        <v/>
+      </c>
+      <c r="T441" t="str">
+        <v/>
+      </c>
+      <c r="U441" t="str">
+        <v/>
+      </c>
+      <c r="V441" t="str">
+        <v/>
+      </c>
+      <c r="W441" t="str">
+        <v/>
+      </c>
+      <c r="X441" t="str">
+        <v/>
+      </c>
+      <c r="Y441" t="str">
+        <v/>
+      </c>
+      <c r="Z441" t="str">
+        <v/>
+      </c>
+      <c r="AA441" t="str">
+        <v/>
+      </c>
+      <c r="AB441" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC441" t="str">
+        <v/>
+      </c>
+      <c r="AD441" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE441" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE440"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE441"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42257,7 +42352,7 @@
         <v>UK</v>
       </c>
       <c r="B2">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="3">
@@ -42409,7 +42504,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B22">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="23">
@@ -42457,7 +42552,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>439</v>
+        <v>440</v>
       </c>
     </row>
     <row r="30">
@@ -42465,7 +42560,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-16</v>
+        <v>2026-10-17</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -41382,10 +41382,10 @@
         <v>Saturday</v>
       </c>
       <c r="C432" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="D432" t="str">
-        <v>London</v>
+        <v>Oxford</v>
       </c>
       <c r="E432" t="str">
         <v>UK</v>
@@ -41394,19 +41394,19 @@
         <v/>
       </c>
       <c r="G432" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST</v>
       </c>
       <c r="H432" t="str">
-        <v/>
+        <v>51.7329316</v>
       </c>
       <c r="I432" t="str">
-        <v/>
+        <v>-1.2373337</v>
       </c>
       <c r="J432" t="str">
-        <v/>
+        <v>2026-10-17 09:31:40 BST</v>
       </c>
       <c r="K432" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L432" t="str">
         <v/>
@@ -41415,19 +41415,19 @@
         <v/>
       </c>
       <c r="N432" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O432" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="P432" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q432" t="str">
-        <v/>
+        <v>51.73293, -1.23733</v>
       </c>
       <c r="R432" t="str">
-        <v/>
+        <v>2026-10-17 09:31:40 BST</v>
       </c>
       <c r="S432" t="str">
         <v/>
@@ -41442,13 +41442,13 @@
         <v/>
       </c>
       <c r="W432" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X432" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y432" t="str">
-        <v/>
+        <v>09:31 UK Oxford, UK</v>
       </c>
       <c r="Z432" t="str">
         <v/>
@@ -41460,7 +41460,7 @@
         <v>flight-inference: BA591→BA590</v>
       </c>
       <c r="AC432" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD432" t="str">
         <v>Yes</v>
@@ -42560,7 +42560,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-17</v>
+        <v>2026-10-18</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -41394,7 +41394,7 @@
         <v/>
       </c>
       <c r="G432" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST</v>
       </c>
       <c r="H432" t="str">
         <v>51.7329316</v>
@@ -41477,10 +41477,10 @@
         <v>Sunday</v>
       </c>
       <c r="C433" t="str">
-        <v/>
+        <v>Woodlands Road</v>
       </c>
       <c r="D433" t="str">
-        <v>London</v>
+        <v>South Oxfordshire</v>
       </c>
       <c r="E433" t="str">
         <v>UK</v>
@@ -41489,19 +41489,19 @@
         <v>BA590</v>
       </c>
       <c r="G433" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule). | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST</v>
       </c>
       <c r="H433" t="str">
-        <v/>
+        <v>51.5212229</v>
       </c>
       <c r="I433" t="str">
-        <v/>
+        <v>-0.9045813</v>
       </c>
       <c r="J433" t="str">
-        <v/>
+        <v>2026-10-18 13:06:06 BST</v>
       </c>
       <c r="K433" t="str">
-        <v/>
+        <v>bracket-inference</v>
       </c>
       <c r="L433" t="str">
         <v/>
@@ -41510,43 +41510,43 @@
         <v/>
       </c>
       <c r="N433" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O433" t="str">
-        <v/>
+        <v>South Oxfordshire</v>
       </c>
       <c r="P433" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q433" t="str">
-        <v/>
+        <v>51.52122, -0.90458</v>
       </c>
       <c r="R433" t="str">
-        <v/>
+        <v>2026-10-18 13:06:06 BST</v>
       </c>
       <c r="S433" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="T433" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="U433" t="str">
-        <v/>
+        <v>51.73298, -1.23729</v>
       </c>
       <c r="V433" t="str">
-        <v/>
+        <v>2026-10-19 07:32:03 BST</v>
       </c>
       <c r="W433" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X433" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y433" t="str">
-        <v/>
+        <v>13:06 UK South Oxfordshire, UK</v>
       </c>
       <c r="Z433" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA433" t="str">
         <v/>
@@ -41555,7 +41555,7 @@
         <v>flight-inference: BA591→BA590 | calendar: Flight BA590: LHR - MXP, departs 20:40 | flight-inference: BA847→BA584</v>
       </c>
       <c r="AC433" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD433" t="str">
         <v>Yes</v>
@@ -41608,16 +41608,16 @@
         <v>Booking</v>
       </c>
       <c r="O434" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="P434" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q434" t="str">
-        <v/>
+        <v>51.73298, -1.23729</v>
       </c>
       <c r="R434" t="str">
-        <v/>
+        <v>2026-10-19 07:32:03 BST</v>
       </c>
       <c r="S434" t="str">
         <v/>
@@ -41635,10 +41635,10 @@
         <v/>
       </c>
       <c r="X434" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y434" t="str">
-        <v/>
+        <v>07:32 UK Oxford, UK</v>
       </c>
       <c r="Z434" t="str">
         <v/>
@@ -42560,7 +42560,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-18</v>
+        <v>2026-10-19</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -41394,7 +41394,7 @@
         <v/>
       </c>
       <c r="G432" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST | Inferred from evening bracket at known location: Oxford 2026-10-17 09:31:40 BST</v>
       </c>
       <c r="H432" t="str">
         <v>51.7329316</v>
@@ -41489,7 +41489,7 @@
         <v>BA590</v>
       </c>
       <c r="G433" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule). | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule). | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST</v>
       </c>
       <c r="H433" t="str">
         <v>51.5212229</v>
@@ -41614,34 +41614,34 @@
         <v>UK</v>
       </c>
       <c r="Q434" t="str">
-        <v>51.73298, -1.23729</v>
+        <v>51.75083, -1.19567</v>
       </c>
       <c r="R434" t="str">
-        <v>2026-10-19 07:32:03 BST</v>
+        <v>2026-10-19 14:41:46 BST</v>
       </c>
       <c r="S434" t="str">
-        <v/>
+        <v>Greater London</v>
       </c>
       <c r="T434" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="U434" t="str">
-        <v/>
+        <v>51.47388, -0.49174</v>
       </c>
       <c r="V434" t="str">
-        <v/>
+        <v>2026-10-20 07:11:31 BST</v>
       </c>
       <c r="W434" t="str">
         <v/>
       </c>
       <c r="X434" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y434" t="str">
-        <v>07:32 UK Oxford, UK</v>
+        <v>07:32 UK Oxford, UK | 14:41 UK Oxford, UK</v>
       </c>
       <c r="Z434" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA434" t="str">
         <v/>
@@ -41703,16 +41703,16 @@
         <v>Booking</v>
       </c>
       <c r="O435" t="str">
-        <v/>
+        <v>Greater London</v>
       </c>
       <c r="P435" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q435" t="str">
-        <v/>
+        <v>51.47388, -0.49174</v>
       </c>
       <c r="R435" t="str">
-        <v/>
+        <v>2026-10-20 07:11:31 BST</v>
       </c>
       <c r="S435" t="str">
         <v/>
@@ -41730,16 +41730,16 @@
         <v/>
       </c>
       <c r="X435" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y435" t="str">
-        <v/>
+        <v>07:11 UK Greater London, UK</v>
       </c>
       <c r="Z435" t="str">
         <v/>
       </c>
       <c r="AA435" t="str">
-        <v/>
+        <v>Flight says Italy; GPS brackets differ (ev=UK, am=-) — kept flight country, please confirm</v>
       </c>
       <c r="AB435" t="str">
         <v>calendar: Flight BA590: LHR - MXP, departs 20:40 | calendar: Flight BA584: LHR - MXP, departs 10:35</v>
@@ -42560,7 +42560,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-19</v>
+        <v>2026-10-20</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE441"/>
+  <dimension ref="A1:AE442"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41489,7 +41489,7 @@
         <v>BA590</v>
       </c>
       <c r="G433" t="str">
-        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule). | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST</v>
+        <v>Flight-inferred country UK from BA591→BA590 stay — night between arrival and return flight (UK midnight rule). | Flight-inferred country UK from BA847→BA584 stay — night between arrival and return flight (UK midnight rule). | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Booking confirmed by evening bracket GPS in same country: South Oxfordshire 2026-10-18 13:06:06 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST | Inferred from GPS brackets: evening=South Oxfordshire 2026-10-18 13:06:06 BST, morning=Oxford 2026-10-19 07:32:03 BST</v>
       </c>
       <c r="H433" t="str">
         <v>51.5212229</v>
@@ -41667,10 +41667,10 @@
         <v>Tuesday</v>
       </c>
       <c r="C435" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D435" t="str">
-        <v>Milan</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E435" t="str">
         <v>Italy</v>
@@ -41682,10 +41682,10 @@
         <v/>
       </c>
       <c r="H435" t="str">
-        <v/>
+        <v>45.8436979</v>
       </c>
       <c r="I435" t="str">
-        <v/>
+        <v>9.0666764</v>
       </c>
       <c r="J435" t="str">
         <v/>
@@ -41709,37 +41709,37 @@
         <v>UK</v>
       </c>
       <c r="Q435" t="str">
-        <v>51.47388, -0.49174</v>
+        <v>51.47389, -0.49173</v>
       </c>
       <c r="R435" t="str">
-        <v>2026-10-20 07:11:31 BST</v>
+        <v>2026-10-20 09:19:00 BST</v>
       </c>
       <c r="S435" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="T435" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="U435" t="str">
-        <v/>
+        <v>45.84370, 9.06668</v>
       </c>
       <c r="V435" t="str">
-        <v/>
+        <v>2026-10-21 07:33:15 BST</v>
       </c>
       <c r="W435" t="str">
         <v/>
       </c>
       <c r="X435" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y435" t="str">
-        <v>07:11 UK Greater London, UK</v>
+        <v>07:11 UK Greater London, UK | 09:19 UK Greater London, UK</v>
       </c>
       <c r="Z435" t="str">
         <v/>
       </c>
       <c r="AA435" t="str">
-        <v>Flight says Italy; GPS brackets differ (ev=UK, am=-) — kept flight country, please confirm</v>
+        <v>Flight says Italy; GPS brackets differ (ev=UK, am=Italy) — kept flight country, please confirm</v>
       </c>
       <c r="AB435" t="str">
         <v>calendar: Flight BA590: LHR - MXP, departs 20:40 | calendar: Flight BA584: LHR - MXP, departs 10:35</v>
@@ -41756,37 +41756,37 @@
     </row>
     <row r="436">
       <c r="A436" t="str">
-        <v>2026-11-08</v>
+        <v>2026-10-21</v>
       </c>
       <c r="B436" t="str">
-        <v>Sunday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C436" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D436" t="str">
-        <v>London</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E436" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F436" t="str">
-        <v>WS001</v>
+        <v/>
       </c>
       <c r="G436" t="str">
-        <v/>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST</v>
       </c>
       <c r="H436" t="str">
-        <v/>
+        <v>45.8436979</v>
       </c>
       <c r="I436" t="str">
-        <v/>
+        <v>9.0666764</v>
       </c>
       <c r="J436" t="str">
-        <v/>
+        <v>2026-10-21 07:33:15 BST</v>
       </c>
       <c r="K436" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L436" t="str">
         <v/>
@@ -41795,19 +41795,19 @@
         <v/>
       </c>
       <c r="N436" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O436" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P436" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q436" t="str">
-        <v/>
+        <v>45.84370, 9.06668</v>
       </c>
       <c r="R436" t="str">
-        <v/>
+        <v>2026-10-21 07:33:15 BST</v>
       </c>
       <c r="S436" t="str">
         <v/>
@@ -41822,13 +41822,13 @@
         <v/>
       </c>
       <c r="W436" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X436" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y436" t="str">
-        <v/>
+        <v>07:33 UK/08:33 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z436" t="str">
         <v/>
@@ -41837,13 +41837,13 @@
         <v/>
       </c>
       <c r="AB436" t="str">
-        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+        <v/>
       </c>
       <c r="AC436" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD436" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE436" t="str">
         <v/>
@@ -41851,22 +41851,22 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="B437" t="str">
-        <v>Monday</v>
+        <v>Sunday</v>
       </c>
       <c r="C437" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D437" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>London</v>
       </c>
       <c r="E437" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F437" t="str">
-        <v>WS1160</v>
+        <v>WS001</v>
       </c>
       <c r="G437" t="str">
         <v/>
@@ -41932,7 +41932,7 @@
         <v/>
       </c>
       <c r="AB437" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
       </c>
       <c r="AC437" t="str">
         <v/>
@@ -41946,10 +41946,10 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="B438" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="C438" t="str">
         <v>Fairmont Scottsdale Princess</v>
@@ -41961,7 +41961,7 @@
         <v/>
       </c>
       <c r="F438" t="str">
-        <v/>
+        <v>WS1160</v>
       </c>
       <c r="G438" t="str">
         <v/>
@@ -42027,7 +42027,7 @@
         <v/>
       </c>
       <c r="AB438" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC438" t="str">
         <v/>
@@ -42041,22 +42041,22 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="B439" t="str">
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C439" t="str">
-        <v/>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="D439" t="str">
-        <v>Los Angeles</v>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="E439" t="str">
-        <v>USA</v>
+        <v/>
       </c>
       <c r="F439" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G439" t="str">
         <v/>
@@ -42122,7 +42122,7 @@
         <v/>
       </c>
       <c r="AB439" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC439" t="str">
         <v/>
@@ -42136,22 +42136,22 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>2027-06-04</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B440" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C440" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D440" t="str">
-        <v>Steve Brazier</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E440" t="str">
-        <v/>
+        <v>USA</v>
       </c>
       <c r="F440" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G440" t="str">
         <v/>
@@ -42217,7 +42217,7 @@
         <v/>
       </c>
       <c r="AB440" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC440" t="str">
         <v/>
@@ -42231,10 +42231,10 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="B441" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C441" t="str">
         <v>, Madrid</v>
@@ -42324,9 +42324,104 @@
         <v/>
       </c>
     </row>
+    <row r="442">
+      <c r="A442" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B442" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C442" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D442" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E442" t="str">
+        <v/>
+      </c>
+      <c r="F442" t="str">
+        <v/>
+      </c>
+      <c r="G442" t="str">
+        <v/>
+      </c>
+      <c r="H442" t="str">
+        <v/>
+      </c>
+      <c r="I442" t="str">
+        <v/>
+      </c>
+      <c r="J442" t="str">
+        <v/>
+      </c>
+      <c r="K442" t="str">
+        <v/>
+      </c>
+      <c r="L442" t="str">
+        <v/>
+      </c>
+      <c r="M442" t="str">
+        <v/>
+      </c>
+      <c r="N442" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O442" t="str">
+        <v/>
+      </c>
+      <c r="P442" t="str">
+        <v/>
+      </c>
+      <c r="Q442" t="str">
+        <v/>
+      </c>
+      <c r="R442" t="str">
+        <v/>
+      </c>
+      <c r="S442" t="str">
+        <v/>
+      </c>
+      <c r="T442" t="str">
+        <v/>
+      </c>
+      <c r="U442" t="str">
+        <v/>
+      </c>
+      <c r="V442" t="str">
+        <v/>
+      </c>
+      <c r="W442" t="str">
+        <v/>
+      </c>
+      <c r="X442" t="str">
+        <v/>
+      </c>
+      <c r="Y442" t="str">
+        <v/>
+      </c>
+      <c r="Z442" t="str">
+        <v/>
+      </c>
+      <c r="AA442" t="str">
+        <v/>
+      </c>
+      <c r="AB442" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC442" t="str">
+        <v/>
+      </c>
+      <c r="AD442" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE442" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE441"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE442"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42360,7 +42455,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4">
@@ -42512,7 +42607,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="24">
@@ -42552,7 +42647,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="30">
@@ -42560,7 +42655,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-20</v>
+        <v>2026-10-21</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE442"/>
+  <dimension ref="A1:AE443"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41774,7 +41774,7 @@
         <v/>
       </c>
       <c r="G436" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST</v>
       </c>
       <c r="H436" t="str">
         <v>45.8436979</v>
@@ -41786,7 +41786,7 @@
         <v>2026-10-21 07:33:15 BST</v>
       </c>
       <c r="K436" t="str">
-        <v>single-bracket-inference</v>
+        <v>bracket-inference</v>
       </c>
       <c r="L436" t="str">
         <v/>
@@ -41810,16 +41810,16 @@
         <v>2026-10-21 07:33:15 BST</v>
       </c>
       <c r="S436" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="T436" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="U436" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="V436" t="str">
-        <v/>
+        <v>2026-10-22 08:06:16 BST</v>
       </c>
       <c r="W436" t="str">
         <v>Yes</v>
@@ -41831,7 +41831,7 @@
         <v>07:33 UK/08:33 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z436" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA436" t="str">
         <v/>
@@ -41851,37 +41851,37 @@
     </row>
     <row r="437">
       <c r="A437" t="str">
-        <v>2026-11-08</v>
+        <v>2026-10-22</v>
       </c>
       <c r="B437" t="str">
-        <v>Sunday</v>
+        <v>Thursday</v>
       </c>
       <c r="C437" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D437" t="str">
-        <v>London</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E437" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F437" t="str">
-        <v>WS001</v>
+        <v/>
       </c>
       <c r="G437" t="str">
-        <v/>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST</v>
       </c>
       <c r="H437" t="str">
-        <v/>
+        <v>45.8436488</v>
       </c>
       <c r="I437" t="str">
-        <v/>
+        <v>9.0666601</v>
       </c>
       <c r="J437" t="str">
-        <v/>
+        <v>2026-10-22 08:06:16 BST</v>
       </c>
       <c r="K437" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L437" t="str">
         <v/>
@@ -41890,19 +41890,19 @@
         <v/>
       </c>
       <c r="N437" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O437" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P437" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q437" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R437" t="str">
-        <v/>
+        <v>2026-10-22 08:06:16 BST</v>
       </c>
       <c r="S437" t="str">
         <v/>
@@ -41917,13 +41917,13 @@
         <v/>
       </c>
       <c r="W437" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X437" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y437" t="str">
-        <v/>
+        <v>08:06 UK/09:06 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z437" t="str">
         <v/>
@@ -41932,13 +41932,13 @@
         <v/>
       </c>
       <c r="AB437" t="str">
-        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+        <v/>
       </c>
       <c r="AC437" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD437" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE437" t="str">
         <v/>
@@ -41946,22 +41946,22 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="B438" t="str">
-        <v>Monday</v>
+        <v>Sunday</v>
       </c>
       <c r="C438" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D438" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>London</v>
       </c>
       <c r="E438" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F438" t="str">
-        <v>WS1160</v>
+        <v>WS001</v>
       </c>
       <c r="G438" t="str">
         <v/>
@@ -42027,7 +42027,7 @@
         <v/>
       </c>
       <c r="AB438" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
       </c>
       <c r="AC438" t="str">
         <v/>
@@ -42041,10 +42041,10 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="B439" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="C439" t="str">
         <v>Fairmont Scottsdale Princess</v>
@@ -42056,7 +42056,7 @@
         <v/>
       </c>
       <c r="F439" t="str">
-        <v/>
+        <v>WS1160</v>
       </c>
       <c r="G439" t="str">
         <v/>
@@ -42122,7 +42122,7 @@
         <v/>
       </c>
       <c r="AB439" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC439" t="str">
         <v/>
@@ -42136,22 +42136,22 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="B440" t="str">
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C440" t="str">
-        <v/>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="D440" t="str">
-        <v>Los Angeles</v>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="E440" t="str">
-        <v>USA</v>
+        <v/>
       </c>
       <c r="F440" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G440" t="str">
         <v/>
@@ -42217,7 +42217,7 @@
         <v/>
       </c>
       <c r="AB440" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC440" t="str">
         <v/>
@@ -42231,22 +42231,22 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>2027-06-04</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B441" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C441" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D441" t="str">
-        <v>Steve Brazier</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E441" t="str">
-        <v/>
+        <v>USA</v>
       </c>
       <c r="F441" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G441" t="str">
         <v/>
@@ -42312,7 +42312,7 @@
         <v/>
       </c>
       <c r="AB441" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC441" t="str">
         <v/>
@@ -42326,10 +42326,10 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="B442" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C442" t="str">
         <v>, Madrid</v>
@@ -42419,9 +42419,104 @@
         <v/>
       </c>
     </row>
+    <row r="443">
+      <c r="A443" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B443" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C443" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D443" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E443" t="str">
+        <v/>
+      </c>
+      <c r="F443" t="str">
+        <v/>
+      </c>
+      <c r="G443" t="str">
+        <v/>
+      </c>
+      <c r="H443" t="str">
+        <v/>
+      </c>
+      <c r="I443" t="str">
+        <v/>
+      </c>
+      <c r="J443" t="str">
+        <v/>
+      </c>
+      <c r="K443" t="str">
+        <v/>
+      </c>
+      <c r="L443" t="str">
+        <v/>
+      </c>
+      <c r="M443" t="str">
+        <v/>
+      </c>
+      <c r="N443" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O443" t="str">
+        <v/>
+      </c>
+      <c r="P443" t="str">
+        <v/>
+      </c>
+      <c r="Q443" t="str">
+        <v/>
+      </c>
+      <c r="R443" t="str">
+        <v/>
+      </c>
+      <c r="S443" t="str">
+        <v/>
+      </c>
+      <c r="T443" t="str">
+        <v/>
+      </c>
+      <c r="U443" t="str">
+        <v/>
+      </c>
+      <c r="V443" t="str">
+        <v/>
+      </c>
+      <c r="W443" t="str">
+        <v/>
+      </c>
+      <c r="X443" t="str">
+        <v/>
+      </c>
+      <c r="Y443" t="str">
+        <v/>
+      </c>
+      <c r="Z443" t="str">
+        <v/>
+      </c>
+      <c r="AA443" t="str">
+        <v/>
+      </c>
+      <c r="AB443" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC443" t="str">
+        <v/>
+      </c>
+      <c r="AD443" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE443" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE442"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE443"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42455,7 +42550,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="4">
@@ -42607,7 +42702,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="24">
@@ -42647,7 +42742,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="30">
@@ -42655,7 +42750,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-21</v>
+        <v>2026-10-22</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -41774,7 +41774,7 @@
         <v/>
       </c>
       <c r="G436" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST</v>
       </c>
       <c r="H436" t="str">
         <v>45.8436979</v>
@@ -41869,16 +41869,16 @@
         <v/>
       </c>
       <c r="G437" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST</v>
       </c>
       <c r="H437" t="str">
-        <v>45.8436488</v>
+        <v>45.8437617</v>
       </c>
       <c r="I437" t="str">
-        <v>9.0666601</v>
+        <v>9.0710045</v>
       </c>
       <c r="J437" t="str">
-        <v>2026-10-22 08:06:16 BST</v>
+        <v>2026-10-22 18:05:21 BST</v>
       </c>
       <c r="K437" t="str">
         <v>single-bracket-inference</v>
@@ -41899,10 +41899,10 @@
         <v>Italy</v>
       </c>
       <c r="Q437" t="str">
-        <v>45.84365, 9.06666</v>
+        <v>45.84376, 9.07100</v>
       </c>
       <c r="R437" t="str">
-        <v>2026-10-22 08:06:16 BST</v>
+        <v>2026-10-22 18:05:21 BST</v>
       </c>
       <c r="S437" t="str">
         <v/>
@@ -41920,13 +41920,13 @@
         <v>Yes</v>
       </c>
       <c r="X437" t="str">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y437" t="str">
-        <v>08:06 UK/09:06 Europe/Rome Cernobbio, Italy</v>
+        <v>08:06 UK/09:06 Europe/Rome Cernobbio, Italy | 18:05 UK/19:05 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z437" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA437" t="str">
         <v/>
@@ -42750,7 +42750,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-22</v>
+        <v>2026-10-23</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE443"/>
+  <dimension ref="A1:AE445"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41774,7 +41774,7 @@
         <v/>
       </c>
       <c r="G436" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-21 07:33:15 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST | Inferred from GPS brackets: evening=Cernobbio 2026-10-21 07:33:15 BST, morning=Cernobbio 2026-10-22 08:06:16 BST</v>
       </c>
       <c r="H436" t="str">
         <v>45.8436979</v>
@@ -41869,7 +41869,7 @@
         <v/>
       </c>
       <c r="G437" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST</v>
       </c>
       <c r="H437" t="str">
         <v>45.8437617</v>
@@ -41946,37 +41946,37 @@
     </row>
     <row r="438">
       <c r="A438" t="str">
-        <v>2026-11-08</v>
+        <v>2026-10-23</v>
       </c>
       <c r="B438" t="str">
-        <v>Sunday</v>
+        <v>Friday</v>
       </c>
       <c r="C438" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D438" t="str">
-        <v>London</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E438" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F438" t="str">
-        <v>WS001</v>
+        <v/>
       </c>
       <c r="G438" t="str">
-        <v/>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST</v>
       </c>
       <c r="H438" t="str">
-        <v/>
+        <v>45.8436511</v>
       </c>
       <c r="I438" t="str">
-        <v/>
+        <v>9.0666561</v>
       </c>
       <c r="J438" t="str">
-        <v/>
+        <v>2026-10-23 23:09:02 BST</v>
       </c>
       <c r="K438" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L438" t="str">
         <v/>
@@ -41985,19 +41985,19 @@
         <v/>
       </c>
       <c r="N438" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O438" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P438" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q438" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R438" t="str">
-        <v/>
+        <v>2026-10-23 23:09:02 BST</v>
       </c>
       <c r="S438" t="str">
         <v/>
@@ -42012,28 +42012,28 @@
         <v/>
       </c>
       <c r="W438" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X438" t="str">
-        <v/>
+        <v>3</v>
       </c>
       <c r="Y438" t="str">
-        <v/>
+        <v>10:26 UK/11:26 Europe/Rome Cernobbio, Italy | 17:46 UK/18:46 Europe/Rome Cernobbio, Italy | 23:09 UK/00:09 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z438" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA438" t="str">
         <v/>
       </c>
       <c r="AB438" t="str">
-        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+        <v/>
       </c>
       <c r="AC438" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD438" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE438" t="str">
         <v/>
@@ -42041,22 +42041,22 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="B439" t="str">
-        <v>Monday</v>
+        <v>Sunday</v>
       </c>
       <c r="C439" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D439" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>London</v>
       </c>
       <c r="E439" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F439" t="str">
-        <v>WS1160</v>
+        <v>WS001</v>
       </c>
       <c r="G439" t="str">
         <v/>
@@ -42122,7 +42122,7 @@
         <v/>
       </c>
       <c r="AB439" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
       </c>
       <c r="AC439" t="str">
         <v/>
@@ -42136,10 +42136,10 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="B440" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="C440" t="str">
         <v>Fairmont Scottsdale Princess</v>
@@ -42151,7 +42151,7 @@
         <v/>
       </c>
       <c r="F440" t="str">
-        <v/>
+        <v>WS1160</v>
       </c>
       <c r="G440" t="str">
         <v/>
@@ -42217,7 +42217,7 @@
         <v/>
       </c>
       <c r="AB440" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC440" t="str">
         <v/>
@@ -42231,22 +42231,22 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="B441" t="str">
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C441" t="str">
-        <v/>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="D441" t="str">
-        <v>Los Angeles</v>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="E441" t="str">
-        <v>USA</v>
+        <v/>
       </c>
       <c r="F441" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G441" t="str">
         <v/>
@@ -42312,7 +42312,7 @@
         <v/>
       </c>
       <c r="AB441" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC441" t="str">
         <v/>
@@ -42326,22 +42326,22 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>2027-06-04</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B442" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C442" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D442" t="str">
-        <v>Steve Brazier</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E442" t="str">
-        <v/>
+        <v>USA</v>
       </c>
       <c r="F442" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G442" t="str">
         <v/>
@@ -42407,7 +42407,7 @@
         <v/>
       </c>
       <c r="AB442" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC442" t="str">
         <v/>
@@ -42421,19 +42421,19 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>2027-06-05</v>
+        <v>2026-12-16</v>
       </c>
       <c r="B443" t="str">
-        <v>Saturday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C443" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D443" t="str">
-        <v>Steve Brazier</v>
+        <v>Bangkok</v>
       </c>
       <c r="E443" t="str">
-        <v/>
+        <v>Thailand</v>
       </c>
       <c r="F443" t="str">
         <v/>
@@ -42502,21 +42502,211 @@
         <v/>
       </c>
       <c r="AB443" t="str">
+        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
+      </c>
+      <c r="AC443" t="str">
+        <v/>
+      </c>
+      <c r="AD443" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE443" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="str">
+        <v>2027-06-04</v>
+      </c>
+      <c r="B444" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="C444" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D444" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E444" t="str">
+        <v/>
+      </c>
+      <c r="F444" t="str">
+        <v/>
+      </c>
+      <c r="G444" t="str">
+        <v/>
+      </c>
+      <c r="H444" t="str">
+        <v/>
+      </c>
+      <c r="I444" t="str">
+        <v/>
+      </c>
+      <c r="J444" t="str">
+        <v/>
+      </c>
+      <c r="K444" t="str">
+        <v/>
+      </c>
+      <c r="L444" t="str">
+        <v/>
+      </c>
+      <c r="M444" t="str">
+        <v/>
+      </c>
+      <c r="N444" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O444" t="str">
+        <v/>
+      </c>
+      <c r="P444" t="str">
+        <v/>
+      </c>
+      <c r="Q444" t="str">
+        <v/>
+      </c>
+      <c r="R444" t="str">
+        <v/>
+      </c>
+      <c r="S444" t="str">
+        <v/>
+      </c>
+      <c r="T444" t="str">
+        <v/>
+      </c>
+      <c r="U444" t="str">
+        <v/>
+      </c>
+      <c r="V444" t="str">
+        <v/>
+      </c>
+      <c r="W444" t="str">
+        <v/>
+      </c>
+      <c r="X444" t="str">
+        <v/>
+      </c>
+      <c r="Y444" t="str">
+        <v/>
+      </c>
+      <c r="Z444" t="str">
+        <v/>
+      </c>
+      <c r="AA444" t="str">
+        <v/>
+      </c>
+      <c r="AB444" t="str">
         <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
       </c>
-      <c r="AC443" t="str">
-        <v/>
-      </c>
-      <c r="AD443" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="AE443" t="str">
+      <c r="AC444" t="str">
+        <v/>
+      </c>
+      <c r="AD444" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE444" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B445" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C445" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D445" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E445" t="str">
+        <v/>
+      </c>
+      <c r="F445" t="str">
+        <v/>
+      </c>
+      <c r="G445" t="str">
+        <v/>
+      </c>
+      <c r="H445" t="str">
+        <v/>
+      </c>
+      <c r="I445" t="str">
+        <v/>
+      </c>
+      <c r="J445" t="str">
+        <v/>
+      </c>
+      <c r="K445" t="str">
+        <v/>
+      </c>
+      <c r="L445" t="str">
+        <v/>
+      </c>
+      <c r="M445" t="str">
+        <v/>
+      </c>
+      <c r="N445" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O445" t="str">
+        <v/>
+      </c>
+      <c r="P445" t="str">
+        <v/>
+      </c>
+      <c r="Q445" t="str">
+        <v/>
+      </c>
+      <c r="R445" t="str">
+        <v/>
+      </c>
+      <c r="S445" t="str">
+        <v/>
+      </c>
+      <c r="T445" t="str">
+        <v/>
+      </c>
+      <c r="U445" t="str">
+        <v/>
+      </c>
+      <c r="V445" t="str">
+        <v/>
+      </c>
+      <c r="W445" t="str">
+        <v/>
+      </c>
+      <c r="X445" t="str">
+        <v/>
+      </c>
+      <c r="Y445" t="str">
+        <v/>
+      </c>
+      <c r="Z445" t="str">
+        <v/>
+      </c>
+      <c r="AA445" t="str">
+        <v/>
+      </c>
+      <c r="AB445" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC445" t="str">
+        <v/>
+      </c>
+      <c r="AD445" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE445" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE443"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE445"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42550,7 +42740,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
@@ -42558,7 +42748,7 @@
         <v>Thailand</v>
       </c>
       <c r="B4">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="5">
@@ -42702,7 +42892,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="24">
@@ -42742,7 +42932,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="30">
@@ -42750,7 +42940,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-23</v>
+        <v>2026-10-24</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE445"/>
+  <dimension ref="A1:AE446"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41869,7 +41869,7 @@
         <v/>
       </c>
       <c r="G437" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 08:06:16 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-22 18:05:21 BST</v>
       </c>
       <c r="H437" t="str">
         <v>45.8437617</v>
@@ -41964,7 +41964,7 @@
         <v/>
       </c>
       <c r="G438" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST</v>
       </c>
       <c r="H438" t="str">
         <v>45.8436511</v>
@@ -42041,22 +42041,22 @@
     </row>
     <row r="439">
       <c r="A439" t="str">
-        <v>2026-11-08</v>
+        <v>2026-10-24</v>
       </c>
       <c r="B439" t="str">
-        <v>Sunday</v>
+        <v>Saturday</v>
       </c>
       <c r="C439" t="str">
         <v/>
       </c>
       <c r="D439" t="str">
-        <v>London</v>
+        <v/>
       </c>
       <c r="E439" t="str">
-        <v>UK</v>
+        <v/>
       </c>
       <c r="F439" t="str">
-        <v>WS001</v>
+        <v/>
       </c>
       <c r="G439" t="str">
         <v/>
@@ -42080,19 +42080,19 @@
         <v/>
       </c>
       <c r="N439" t="str">
-        <v>Booking</v>
+        <v/>
       </c>
       <c r="O439" t="str">
-        <v/>
+        <v>Capiago Intimiano</v>
       </c>
       <c r="P439" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q439" t="str">
-        <v/>
+        <v>45.77765, 9.13539</v>
       </c>
       <c r="R439" t="str">
-        <v/>
+        <v>2026-10-24 15:45:21 BST</v>
       </c>
       <c r="S439" t="str">
         <v/>
@@ -42110,10 +42110,10 @@
         <v/>
       </c>
       <c r="X439" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y439" t="str">
-        <v/>
+        <v>13:08 UK/14:08 Europe/Rome Montorfano, Italy | 15:45 UK/16:45 Europe/Rome Capiago Intimiano, Italy</v>
       </c>
       <c r="Z439" t="str">
         <v/>
@@ -42122,13 +42122,13 @@
         <v/>
       </c>
       <c r="AB439" t="str">
-        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+        <v/>
       </c>
       <c r="AC439" t="str">
         <v/>
       </c>
       <c r="AD439" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE439" t="str">
         <v/>
@@ -42136,22 +42136,22 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="B440" t="str">
-        <v>Monday</v>
+        <v>Sunday</v>
       </c>
       <c r="C440" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D440" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>London</v>
       </c>
       <c r="E440" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F440" t="str">
-        <v>WS1160</v>
+        <v>WS001</v>
       </c>
       <c r="G440" t="str">
         <v/>
@@ -42217,7 +42217,7 @@
         <v/>
       </c>
       <c r="AB440" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
       </c>
       <c r="AC440" t="str">
         <v/>
@@ -42231,10 +42231,10 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="B441" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="C441" t="str">
         <v>Fairmont Scottsdale Princess</v>
@@ -42246,7 +42246,7 @@
         <v/>
       </c>
       <c r="F441" t="str">
-        <v/>
+        <v>WS1160</v>
       </c>
       <c r="G441" t="str">
         <v/>
@@ -42312,7 +42312,7 @@
         <v/>
       </c>
       <c r="AB441" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC441" t="str">
         <v/>
@@ -42326,22 +42326,22 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="B442" t="str">
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C442" t="str">
-        <v/>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="D442" t="str">
-        <v>Los Angeles</v>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="E442" t="str">
-        <v>USA</v>
+        <v/>
       </c>
       <c r="F442" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G442" t="str">
         <v/>
@@ -42407,7 +42407,7 @@
         <v/>
       </c>
       <c r="AB442" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC442" t="str">
         <v/>
@@ -42421,7 +42421,7 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>2026-12-16</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B443" t="str">
         <v>Wednesday</v>
@@ -42430,13 +42430,13 @@
         <v/>
       </c>
       <c r="D443" t="str">
-        <v>Bangkok</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E443" t="str">
-        <v>Thailand</v>
+        <v>USA</v>
       </c>
       <c r="F443" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G443" t="str">
         <v/>
@@ -42502,7 +42502,7 @@
         <v/>
       </c>
       <c r="AB443" t="str">
-        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC443" t="str">
         <v/>
@@ -42516,19 +42516,19 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>2027-06-04</v>
+        <v>2026-12-16</v>
       </c>
       <c r="B444" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C444" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D444" t="str">
-        <v>Steve Brazier</v>
+        <v>Bangkok</v>
       </c>
       <c r="E444" t="str">
-        <v/>
+        <v>Thailand</v>
       </c>
       <c r="F444" t="str">
         <v/>
@@ -42597,7 +42597,7 @@
         <v/>
       </c>
       <c r="AB444" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
       </c>
       <c r="AC444" t="str">
         <v/>
@@ -42611,10 +42611,10 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="B445" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C445" t="str">
         <v>, Madrid</v>
@@ -42704,9 +42704,104 @@
         <v/>
       </c>
     </row>
+    <row r="446">
+      <c r="A446" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B446" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C446" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D446" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E446" t="str">
+        <v/>
+      </c>
+      <c r="F446" t="str">
+        <v/>
+      </c>
+      <c r="G446" t="str">
+        <v/>
+      </c>
+      <c r="H446" t="str">
+        <v/>
+      </c>
+      <c r="I446" t="str">
+        <v/>
+      </c>
+      <c r="J446" t="str">
+        <v/>
+      </c>
+      <c r="K446" t="str">
+        <v/>
+      </c>
+      <c r="L446" t="str">
+        <v/>
+      </c>
+      <c r="M446" t="str">
+        <v/>
+      </c>
+      <c r="N446" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O446" t="str">
+        <v/>
+      </c>
+      <c r="P446" t="str">
+        <v/>
+      </c>
+      <c r="Q446" t="str">
+        <v/>
+      </c>
+      <c r="R446" t="str">
+        <v/>
+      </c>
+      <c r="S446" t="str">
+        <v/>
+      </c>
+      <c r="T446" t="str">
+        <v/>
+      </c>
+      <c r="U446" t="str">
+        <v/>
+      </c>
+      <c r="V446" t="str">
+        <v/>
+      </c>
+      <c r="W446" t="str">
+        <v/>
+      </c>
+      <c r="X446" t="str">
+        <v/>
+      </c>
+      <c r="Y446" t="str">
+        <v/>
+      </c>
+      <c r="Z446" t="str">
+        <v/>
+      </c>
+      <c r="AA446" t="str">
+        <v/>
+      </c>
+      <c r="AB446" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC446" t="str">
+        <v/>
+      </c>
+      <c r="AD446" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE446" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE445"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE446"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42756,7 +42851,7 @@
         <v>Unrecorded</v>
       </c>
       <c r="B5">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6">
@@ -42932,7 +43027,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>444</v>
+        <v>445</v>
       </c>
     </row>
     <row r="30">
@@ -42940,7 +43035,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-24</v>
+        <v>2026-10-25</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE446"/>
+  <dimension ref="A1:AE447"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -41964,7 +41964,7 @@
         <v/>
       </c>
       <c r="G438" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 10:26:41 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 17:46:25 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST | Inferred from evening bracket at known location: Cernobbio 2026-10-23 23:09:02 BST</v>
       </c>
       <c r="H438" t="str">
         <v>45.8436511</v>
@@ -42047,13 +42047,13 @@
         <v>Saturday</v>
       </c>
       <c r="C439" t="str">
-        <v/>
+        <v>Golf Villa D'Este</v>
       </c>
       <c r="D439" t="str">
-        <v/>
+        <v>Capiago Intimiano</v>
       </c>
       <c r="E439" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="F439" t="str">
         <v/>
@@ -42062,16 +42062,16 @@
         <v/>
       </c>
       <c r="H439" t="str">
-        <v/>
+        <v>45.7776497</v>
       </c>
       <c r="I439" t="str">
-        <v/>
+        <v>9.135393</v>
       </c>
       <c r="J439" t="str">
-        <v/>
+        <v>2026-10-24 15:45:21 BST</v>
       </c>
       <c r="K439" t="str">
-        <v/>
+        <v>single-bracket-reconcile</v>
       </c>
       <c r="L439" t="str">
         <v/>
@@ -42080,7 +42080,7 @@
         <v/>
       </c>
       <c r="N439" t="str">
-        <v/>
+        <v>Bracket GPS</v>
       </c>
       <c r="O439" t="str">
         <v>Capiago Intimiano</v>
@@ -42107,7 +42107,7 @@
         <v/>
       </c>
       <c r="W439" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X439" t="str">
         <v>2</v>
@@ -42136,37 +42136,37 @@
     </row>
     <row r="440">
       <c r="A440" t="str">
-        <v>2026-11-08</v>
+        <v>2026-10-25</v>
       </c>
       <c r="B440" t="str">
         <v>Sunday</v>
       </c>
       <c r="C440" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D440" t="str">
-        <v>London</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E440" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F440" t="str">
-        <v>WS001</v>
+        <v/>
       </c>
       <c r="G440" t="str">
-        <v/>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0</v>
       </c>
       <c r="H440" t="str">
-        <v/>
+        <v>45.8436503</v>
       </c>
       <c r="I440" t="str">
-        <v/>
+        <v>9.066661</v>
       </c>
       <c r="J440" t="str">
-        <v/>
+        <v>2026-10-25 12:04:47 GMT+0</v>
       </c>
       <c r="K440" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L440" t="str">
         <v/>
@@ -42175,19 +42175,19 @@
         <v/>
       </c>
       <c r="N440" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O440" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P440" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q440" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R440" t="str">
-        <v/>
+        <v>2026-10-25 12:04:47 GMT+0</v>
       </c>
       <c r="S440" t="str">
         <v/>
@@ -42202,13 +42202,13 @@
         <v/>
       </c>
       <c r="W440" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X440" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y440" t="str">
-        <v/>
+        <v>12:04 UK/13:04 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z440" t="str">
         <v/>
@@ -42217,13 +42217,13 @@
         <v/>
       </c>
       <c r="AB440" t="str">
-        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+        <v/>
       </c>
       <c r="AC440" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD440" t="str">
-        <v>Yes</v>
+        <v/>
       </c>
       <c r="AE440" t="str">
         <v/>
@@ -42231,22 +42231,22 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>2026-11-09</v>
+        <v>2026-11-08</v>
       </c>
       <c r="B441" t="str">
-        <v>Monday</v>
+        <v>Sunday</v>
       </c>
       <c r="C441" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D441" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>London</v>
       </c>
       <c r="E441" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F441" t="str">
-        <v>WS1160</v>
+        <v>WS001</v>
       </c>
       <c r="G441" t="str">
         <v/>
@@ -42312,7 +42312,7 @@
         <v/>
       </c>
       <c r="AB441" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
       </c>
       <c r="AC441" t="str">
         <v/>
@@ -42326,10 +42326,10 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>2026-11-10</v>
+        <v>2026-11-09</v>
       </c>
       <c r="B442" t="str">
-        <v>Tuesday</v>
+        <v>Monday</v>
       </c>
       <c r="C442" t="str">
         <v>Fairmont Scottsdale Princess</v>
@@ -42341,7 +42341,7 @@
         <v/>
       </c>
       <c r="F442" t="str">
-        <v/>
+        <v>WS1160</v>
       </c>
       <c r="G442" t="str">
         <v/>
@@ -42407,7 +42407,7 @@
         <v/>
       </c>
       <c r="AB442" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC442" t="str">
         <v/>
@@ -42421,22 +42421,22 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>2026-11-11</v>
+        <v>2026-11-10</v>
       </c>
       <c r="B443" t="str">
-        <v>Wednesday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C443" t="str">
-        <v/>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="D443" t="str">
-        <v>Los Angeles</v>
+        <v>Fairmont Scottsdale Princess</v>
       </c>
       <c r="E443" t="str">
-        <v>USA</v>
+        <v/>
       </c>
       <c r="F443" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G443" t="str">
         <v/>
@@ -42502,7 +42502,7 @@
         <v/>
       </c>
       <c r="AB443" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
       </c>
       <c r="AC443" t="str">
         <v/>
@@ -42516,7 +42516,7 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>2026-12-16</v>
+        <v>2026-11-11</v>
       </c>
       <c r="B444" t="str">
         <v>Wednesday</v>
@@ -42525,13 +42525,13 @@
         <v/>
       </c>
       <c r="D444" t="str">
-        <v>Bangkok</v>
+        <v>Los Angeles</v>
       </c>
       <c r="E444" t="str">
-        <v>Thailand</v>
+        <v>USA</v>
       </c>
       <c r="F444" t="str">
-        <v/>
+        <v>UA5959, UA820</v>
       </c>
       <c r="G444" t="str">
         <v/>
@@ -42597,7 +42597,7 @@
         <v/>
       </c>
       <c r="AB444" t="str">
-        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
       </c>
       <c r="AC444" t="str">
         <v/>
@@ -42611,19 +42611,19 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>2027-06-04</v>
+        <v>2026-12-16</v>
       </c>
       <c r="B445" t="str">
-        <v>Friday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C445" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D445" t="str">
-        <v>Steve Brazier</v>
+        <v>Bangkok</v>
       </c>
       <c r="E445" t="str">
-        <v/>
+        <v>Thailand</v>
       </c>
       <c r="F445" t="str">
         <v/>
@@ -42692,7 +42692,7 @@
         <v/>
       </c>
       <c r="AB445" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
       </c>
       <c r="AC445" t="str">
         <v/>
@@ -42706,10 +42706,10 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>2027-06-05</v>
+        <v>2027-06-04</v>
       </c>
       <c r="B446" t="str">
-        <v>Saturday</v>
+        <v>Friday</v>
       </c>
       <c r="C446" t="str">
         <v>, Madrid</v>
@@ -42799,9 +42799,104 @@
         <v/>
       </c>
     </row>
+    <row r="447">
+      <c r="A447" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B447" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C447" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D447" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E447" t="str">
+        <v/>
+      </c>
+      <c r="F447" t="str">
+        <v/>
+      </c>
+      <c r="G447" t="str">
+        <v/>
+      </c>
+      <c r="H447" t="str">
+        <v/>
+      </c>
+      <c r="I447" t="str">
+        <v/>
+      </c>
+      <c r="J447" t="str">
+        <v/>
+      </c>
+      <c r="K447" t="str">
+        <v/>
+      </c>
+      <c r="L447" t="str">
+        <v/>
+      </c>
+      <c r="M447" t="str">
+        <v/>
+      </c>
+      <c r="N447" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O447" t="str">
+        <v/>
+      </c>
+      <c r="P447" t="str">
+        <v/>
+      </c>
+      <c r="Q447" t="str">
+        <v/>
+      </c>
+      <c r="R447" t="str">
+        <v/>
+      </c>
+      <c r="S447" t="str">
+        <v/>
+      </c>
+      <c r="T447" t="str">
+        <v/>
+      </c>
+      <c r="U447" t="str">
+        <v/>
+      </c>
+      <c r="V447" t="str">
+        <v/>
+      </c>
+      <c r="W447" t="str">
+        <v/>
+      </c>
+      <c r="X447" t="str">
+        <v/>
+      </c>
+      <c r="Y447" t="str">
+        <v/>
+      </c>
+      <c r="Z447" t="str">
+        <v/>
+      </c>
+      <c r="AA447" t="str">
+        <v/>
+      </c>
+      <c r="AB447" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC447" t="str">
+        <v/>
+      </c>
+      <c r="AD447" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE447" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE446"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE447"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42835,7 +42930,7 @@
         <v>Italy</v>
       </c>
       <c r="B3">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="4">
@@ -42851,7 +42946,7 @@
         <v>Unrecorded</v>
       </c>
       <c r="B5">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
@@ -42987,7 +43082,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="24">
@@ -43027,7 +43122,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="30">
@@ -43035,7 +43130,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-25</v>
+        <v>2026-10-26</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE447"/>
+  <dimension ref="A1:AE455"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="10.83203125" customWidth="1"/>
@@ -42059,7 +42059,7 @@
         <v/>
       </c>
       <c r="G439" t="str">
-        <v/>
+        <v>Booking confirmed by evening bracket GPS in same country: Capiago Intimiano 2026-10-24 15:45:21 BST</v>
       </c>
       <c r="H439" t="str">
         <v>45.7776497</v>
@@ -42071,7 +42071,7 @@
         <v>2026-10-24 15:45:21 BST</v>
       </c>
       <c r="K439" t="str">
-        <v>single-bracket-reconcile</v>
+        <v>bracket-booking-inference</v>
       </c>
       <c r="L439" t="str">
         <v/>
@@ -42122,13 +42122,13 @@
         <v/>
       </c>
       <c r="AB439" t="str">
-        <v/>
+        <v>flight-inference: BA584→BA581</v>
       </c>
       <c r="AC439" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD439" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AE439" t="str">
         <v/>
@@ -42154,7 +42154,7 @@
         <v/>
       </c>
       <c r="G440" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0</v>
       </c>
       <c r="H440" t="str">
         <v>45.8436503</v>
@@ -42231,37 +42231,37 @@
     </row>
     <row r="441">
       <c r="A441" t="str">
-        <v>2026-11-08</v>
+        <v>2026-10-26</v>
       </c>
       <c r="B441" t="str">
-        <v>Sunday</v>
+        <v>Monday</v>
       </c>
       <c r="C441" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D441" t="str">
-        <v>London</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E441" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="F441" t="str">
-        <v>WS001</v>
+        <v/>
       </c>
       <c r="G441" t="str">
-        <v/>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0</v>
       </c>
       <c r="H441" t="str">
-        <v/>
+        <v>45.8436497</v>
       </c>
       <c r="I441" t="str">
-        <v/>
+        <v>9.0666591</v>
       </c>
       <c r="J441" t="str">
-        <v/>
+        <v>2026-10-26 19:57:13 GMT+0</v>
       </c>
       <c r="K441" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L441" t="str">
         <v/>
@@ -42270,19 +42270,19 @@
         <v/>
       </c>
       <c r="N441" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O441" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P441" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q441" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R441" t="str">
-        <v/>
+        <v>2026-10-26 19:57:13 GMT+0</v>
       </c>
       <c r="S441" t="str">
         <v/>
@@ -42297,13 +42297,13 @@
         <v/>
       </c>
       <c r="W441" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X441" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y441" t="str">
-        <v/>
+        <v>19:57 UK/20:57 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z441" t="str">
         <v/>
@@ -42312,10 +42312,10 @@
         <v/>
       </c>
       <c r="AB441" t="str">
-        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+        <v>flight-inference: BA584→BA581</v>
       </c>
       <c r="AC441" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD441" t="str">
         <v>Yes</v>
@@ -42326,25 +42326,25 @@
     </row>
     <row r="442">
       <c r="A442" t="str">
-        <v>2026-11-09</v>
+        <v>2026-10-27</v>
       </c>
       <c r="B442" t="str">
-        <v>Monday</v>
+        <v>Tuesday</v>
       </c>
       <c r="C442" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D442" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>Milan</v>
       </c>
       <c r="E442" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="F442" t="str">
-        <v>WS1160</v>
+        <v/>
       </c>
       <c r="G442" t="str">
-        <v/>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule).</v>
       </c>
       <c r="H442" t="str">
         <v/>
@@ -42407,7 +42407,7 @@
         <v/>
       </c>
       <c r="AB442" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+        <v>flight-inference: BA584→BA581</v>
       </c>
       <c r="AC442" t="str">
         <v/>
@@ -42421,25 +42421,25 @@
     </row>
     <row r="443">
       <c r="A443" t="str">
-        <v>2026-11-10</v>
+        <v>2026-10-28</v>
       </c>
       <c r="B443" t="str">
-        <v>Tuesday</v>
+        <v>Wednesday</v>
       </c>
       <c r="C443" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v/>
       </c>
       <c r="D443" t="str">
-        <v>Fairmont Scottsdale Princess</v>
+        <v>Milan</v>
       </c>
       <c r="E443" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="F443" t="str">
         <v/>
       </c>
       <c r="G443" t="str">
-        <v/>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule).</v>
       </c>
       <c r="H443" t="str">
         <v/>
@@ -42502,7 +42502,7 @@
         <v/>
       </c>
       <c r="AB443" t="str">
-        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+        <v>flight-inference: BA584→BA581</v>
       </c>
       <c r="AC443" t="str">
         <v/>
@@ -42516,25 +42516,25 @@
     </row>
     <row r="444">
       <c r="A444" t="str">
-        <v>2026-11-11</v>
+        <v>2026-10-29</v>
       </c>
       <c r="B444" t="str">
-        <v>Wednesday</v>
+        <v>Thursday</v>
       </c>
       <c r="C444" t="str">
         <v/>
       </c>
       <c r="D444" t="str">
-        <v>Los Angeles</v>
+        <v>Milan</v>
       </c>
       <c r="E444" t="str">
-        <v>USA</v>
+        <v>Italy</v>
       </c>
       <c r="F444" t="str">
-        <v>UA5959, UA820</v>
+        <v/>
       </c>
       <c r="G444" t="str">
-        <v/>
+        <v>Flight-inferred country Italy from BA581 direction (UK midnight rule).</v>
       </c>
       <c r="H444" t="str">
         <v/>
@@ -42597,7 +42597,7 @@
         <v/>
       </c>
       <c r="AB444" t="str">
-        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+        <v>flight-inference: BA581</v>
       </c>
       <c r="AC444" t="str">
         <v/>
@@ -42611,22 +42611,22 @@
     </row>
     <row r="445">
       <c r="A445" t="str">
-        <v>2026-12-16</v>
+        <v>2026-10-30</v>
       </c>
       <c r="B445" t="str">
-        <v>Wednesday</v>
+        <v>Friday</v>
       </c>
       <c r="C445" t="str">
         <v/>
       </c>
       <c r="D445" t="str">
-        <v>Bangkok</v>
+        <v>London</v>
       </c>
       <c r="E445" t="str">
-        <v>Thailand</v>
+        <v>UK</v>
       </c>
       <c r="F445" t="str">
-        <v/>
+        <v>BA581</v>
       </c>
       <c r="G445" t="str">
         <v/>
@@ -42692,7 +42692,7 @@
         <v/>
       </c>
       <c r="AB445" t="str">
-        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
+        <v>calendar+email: Flight BA581: MXP - LHR, departs 12:45 | Fw: Your booking confirmation ZRDGS4</v>
       </c>
       <c r="AC445" t="str">
         <v/>
@@ -42706,25 +42706,25 @@
     </row>
     <row r="446">
       <c r="A446" t="str">
-        <v>2027-06-04</v>
+        <v>2026-10-31</v>
       </c>
       <c r="B446" t="str">
-        <v>Friday</v>
+        <v>Saturday</v>
       </c>
       <c r="C446" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D446" t="str">
-        <v>Steve Brazier</v>
+        <v>London</v>
       </c>
       <c r="E446" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F446" t="str">
         <v/>
       </c>
       <c r="G446" t="str">
-        <v/>
+        <v>Flight-inferred country UK from BA581→BA588 stay — night between arrival and return flight (UK midnight rule).</v>
       </c>
       <c r="H446" t="str">
         <v/>
@@ -42787,7 +42787,7 @@
         <v/>
       </c>
       <c r="AB446" t="str">
-        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+        <v>email: Fw: Your booking confirmation ZRDGS4</v>
       </c>
       <c r="AC446" t="str">
         <v/>
@@ -42801,25 +42801,25 @@
     </row>
     <row r="447">
       <c r="A447" t="str">
-        <v>2027-06-05</v>
+        <v>2026-11-01</v>
       </c>
       <c r="B447" t="str">
-        <v>Saturday</v>
+        <v>Sunday</v>
       </c>
       <c r="C447" t="str">
-        <v>, Madrid</v>
+        <v/>
       </c>
       <c r="D447" t="str">
-        <v>Steve Brazier</v>
+        <v>London</v>
       </c>
       <c r="E447" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="F447" t="str">
         <v/>
       </c>
       <c r="G447" t="str">
-        <v/>
+        <v>Flight-inferred country UK from BA588 direction (UK midnight rule).</v>
       </c>
       <c r="H447" t="str">
         <v/>
@@ -42882,21 +42882,781 @@
         <v/>
       </c>
       <c r="AB447" t="str">
+        <v>email: Fw: Your booking confirmation ZRDGS4</v>
+      </c>
+      <c r="AC447" t="str">
+        <v/>
+      </c>
+      <c r="AD447" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE447" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="str">
+        <v>2026-11-02</v>
+      </c>
+      <c r="B448" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="C448" t="str">
+        <v/>
+      </c>
+      <c r="D448" t="str">
+        <v>Milan</v>
+      </c>
+      <c r="E448" t="str">
+        <v>Italy</v>
+      </c>
+      <c r="F448" t="str">
+        <v>BA588</v>
+      </c>
+      <c r="G448" t="str">
+        <v/>
+      </c>
+      <c r="H448" t="str">
+        <v/>
+      </c>
+      <c r="I448" t="str">
+        <v/>
+      </c>
+      <c r="J448" t="str">
+        <v/>
+      </c>
+      <c r="K448" t="str">
+        <v/>
+      </c>
+      <c r="L448" t="str">
+        <v/>
+      </c>
+      <c r="M448" t="str">
+        <v/>
+      </c>
+      <c r="N448" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O448" t="str">
+        <v/>
+      </c>
+      <c r="P448" t="str">
+        <v/>
+      </c>
+      <c r="Q448" t="str">
+        <v/>
+      </c>
+      <c r="R448" t="str">
+        <v/>
+      </c>
+      <c r="S448" t="str">
+        <v/>
+      </c>
+      <c r="T448" t="str">
+        <v/>
+      </c>
+      <c r="U448" t="str">
+        <v/>
+      </c>
+      <c r="V448" t="str">
+        <v/>
+      </c>
+      <c r="W448" t="str">
+        <v/>
+      </c>
+      <c r="X448" t="str">
+        <v/>
+      </c>
+      <c r="Y448" t="str">
+        <v/>
+      </c>
+      <c r="Z448" t="str">
+        <v/>
+      </c>
+      <c r="AA448" t="str">
+        <v/>
+      </c>
+      <c r="AB448" t="str">
+        <v>calendar: Flight BA588: LHR - MXP, departs 16:55</v>
+      </c>
+      <c r="AC448" t="str">
+        <v/>
+      </c>
+      <c r="AD448" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE448" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="str">
+        <v>2026-11-08</v>
+      </c>
+      <c r="B449" t="str">
+        <v>Sunday</v>
+      </c>
+      <c r="C449" t="str">
+        <v/>
+      </c>
+      <c r="D449" t="str">
+        <v>London</v>
+      </c>
+      <c r="E449" t="str">
+        <v>UK</v>
+      </c>
+      <c r="F449" t="str">
+        <v>WS001</v>
+      </c>
+      <c r="G449" t="str">
+        <v/>
+      </c>
+      <c r="H449" t="str">
+        <v/>
+      </c>
+      <c r="I449" t="str">
+        <v/>
+      </c>
+      <c r="J449" t="str">
+        <v/>
+      </c>
+      <c r="K449" t="str">
+        <v/>
+      </c>
+      <c r="L449" t="str">
+        <v/>
+      </c>
+      <c r="M449" t="str">
+        <v/>
+      </c>
+      <c r="N449" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O449" t="str">
+        <v/>
+      </c>
+      <c r="P449" t="str">
+        <v/>
+      </c>
+      <c r="Q449" t="str">
+        <v/>
+      </c>
+      <c r="R449" t="str">
+        <v/>
+      </c>
+      <c r="S449" t="str">
+        <v/>
+      </c>
+      <c r="T449" t="str">
+        <v/>
+      </c>
+      <c r="U449" t="str">
+        <v/>
+      </c>
+      <c r="V449" t="str">
+        <v/>
+      </c>
+      <c r="W449" t="str">
+        <v/>
+      </c>
+      <c r="X449" t="str">
+        <v/>
+      </c>
+      <c r="Y449" t="str">
+        <v/>
+      </c>
+      <c r="Z449" t="str">
+        <v/>
+      </c>
+      <c r="AA449" t="str">
+        <v/>
+      </c>
+      <c r="AB449" t="str">
+        <v>calendar: Flight WS001: LHR - Calgary, departs 14:50</v>
+      </c>
+      <c r="AC449" t="str">
+        <v/>
+      </c>
+      <c r="AD449" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE449" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="str">
+        <v>2026-11-09</v>
+      </c>
+      <c r="B450" t="str">
+        <v>Monday</v>
+      </c>
+      <c r="C450" t="str">
+        <v>Fairmont Scottsdale Princess</v>
+      </c>
+      <c r="D450" t="str">
+        <v>Fairmont Scottsdale Princess</v>
+      </c>
+      <c r="E450" t="str">
+        <v/>
+      </c>
+      <c r="F450" t="str">
+        <v>WS1160</v>
+      </c>
+      <c r="G450" t="str">
+        <v/>
+      </c>
+      <c r="H450" t="str">
+        <v/>
+      </c>
+      <c r="I450" t="str">
+        <v/>
+      </c>
+      <c r="J450" t="str">
+        <v/>
+      </c>
+      <c r="K450" t="str">
+        <v/>
+      </c>
+      <c r="L450" t="str">
+        <v/>
+      </c>
+      <c r="M450" t="str">
+        <v/>
+      </c>
+      <c r="N450" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O450" t="str">
+        <v/>
+      </c>
+      <c r="P450" t="str">
+        <v/>
+      </c>
+      <c r="Q450" t="str">
+        <v/>
+      </c>
+      <c r="R450" t="str">
+        <v/>
+      </c>
+      <c r="S450" t="str">
+        <v/>
+      </c>
+      <c r="T450" t="str">
+        <v/>
+      </c>
+      <c r="U450" t="str">
+        <v/>
+      </c>
+      <c r="V450" t="str">
+        <v/>
+      </c>
+      <c r="W450" t="str">
+        <v/>
+      </c>
+      <c r="X450" t="str">
+        <v/>
+      </c>
+      <c r="Y450" t="str">
+        <v/>
+      </c>
+      <c r="Z450" t="str">
+        <v/>
+      </c>
+      <c r="AA450" t="str">
+        <v/>
+      </c>
+      <c r="AB450" t="str">
+        <v>calendar: Hotel: Fairmont Scottsdale Princess | calendar: Flight WS1160: Calgary - Phoenix, departs 09:50  | Hotel: Fairmont Scottsdale Princess</v>
+      </c>
+      <c r="AC450" t="str">
+        <v/>
+      </c>
+      <c r="AD450" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE450" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="str">
+        <v>2026-11-10</v>
+      </c>
+      <c r="B451" t="str">
+        <v>Tuesday</v>
+      </c>
+      <c r="C451" t="str">
+        <v>Fairmont Scottsdale Princess</v>
+      </c>
+      <c r="D451" t="str">
+        <v>Fairmont Scottsdale Princess</v>
+      </c>
+      <c r="E451" t="str">
+        <v/>
+      </c>
+      <c r="F451" t="str">
+        <v/>
+      </c>
+      <c r="G451" t="str">
+        <v/>
+      </c>
+      <c r="H451" t="str">
+        <v/>
+      </c>
+      <c r="I451" t="str">
+        <v/>
+      </c>
+      <c r="J451" t="str">
+        <v/>
+      </c>
+      <c r="K451" t="str">
+        <v/>
+      </c>
+      <c r="L451" t="str">
+        <v/>
+      </c>
+      <c r="M451" t="str">
+        <v/>
+      </c>
+      <c r="N451" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O451" t="str">
+        <v/>
+      </c>
+      <c r="P451" t="str">
+        <v/>
+      </c>
+      <c r="Q451" t="str">
+        <v/>
+      </c>
+      <c r="R451" t="str">
+        <v/>
+      </c>
+      <c r="S451" t="str">
+        <v/>
+      </c>
+      <c r="T451" t="str">
+        <v/>
+      </c>
+      <c r="U451" t="str">
+        <v/>
+      </c>
+      <c r="V451" t="str">
+        <v/>
+      </c>
+      <c r="W451" t="str">
+        <v/>
+      </c>
+      <c r="X451" t="str">
+        <v/>
+      </c>
+      <c r="Y451" t="str">
+        <v/>
+      </c>
+      <c r="Z451" t="str">
+        <v/>
+      </c>
+      <c r="AA451" t="str">
+        <v/>
+      </c>
+      <c r="AB451" t="str">
+        <v>calendar: Hotel: Fairmont Scottsdale Princess</v>
+      </c>
+      <c r="AC451" t="str">
+        <v/>
+      </c>
+      <c r="AD451" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE451" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="str">
+        <v>2026-11-11</v>
+      </c>
+      <c r="B452" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="C452" t="str">
+        <v/>
+      </c>
+      <c r="D452" t="str">
+        <v>Los Angeles</v>
+      </c>
+      <c r="E452" t="str">
+        <v>USA</v>
+      </c>
+      <c r="F452" t="str">
+        <v>UA5959, UA820</v>
+      </c>
+      <c r="G452" t="str">
+        <v/>
+      </c>
+      <c r="H452" t="str">
+        <v/>
+      </c>
+      <c r="I452" t="str">
+        <v/>
+      </c>
+      <c r="J452" t="str">
+        <v/>
+      </c>
+      <c r="K452" t="str">
+        <v/>
+      </c>
+      <c r="L452" t="str">
+        <v/>
+      </c>
+      <c r="M452" t="str">
+        <v/>
+      </c>
+      <c r="N452" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O452" t="str">
+        <v/>
+      </c>
+      <c r="P452" t="str">
+        <v/>
+      </c>
+      <c r="Q452" t="str">
+        <v/>
+      </c>
+      <c r="R452" t="str">
+        <v/>
+      </c>
+      <c r="S452" t="str">
+        <v/>
+      </c>
+      <c r="T452" t="str">
+        <v/>
+      </c>
+      <c r="U452" t="str">
+        <v/>
+      </c>
+      <c r="V452" t="str">
+        <v/>
+      </c>
+      <c r="W452" t="str">
+        <v/>
+      </c>
+      <c r="X452" t="str">
+        <v/>
+      </c>
+      <c r="Y452" t="str">
+        <v/>
+      </c>
+      <c r="Z452" t="str">
+        <v/>
+      </c>
+      <c r="AA452" t="str">
+        <v/>
+      </c>
+      <c r="AB452" t="str">
+        <v>calendar: Flight UA5959: PHX - LAX, departs 17:10</v>
+      </c>
+      <c r="AC452" t="str">
+        <v/>
+      </c>
+      <c r="AD452" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE452" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="str">
+        <v>2026-12-16</v>
+      </c>
+      <c r="B453" t="str">
+        <v>Wednesday</v>
+      </c>
+      <c r="C453" t="str">
+        <v/>
+      </c>
+      <c r="D453" t="str">
+        <v>Bangkok</v>
+      </c>
+      <c r="E453" t="str">
+        <v>Thailand</v>
+      </c>
+      <c r="F453" t="str">
+        <v/>
+      </c>
+      <c r="G453" t="str">
+        <v/>
+      </c>
+      <c r="H453" t="str">
+        <v/>
+      </c>
+      <c r="I453" t="str">
+        <v/>
+      </c>
+      <c r="J453" t="str">
+        <v/>
+      </c>
+      <c r="K453" t="str">
+        <v/>
+      </c>
+      <c r="L453" t="str">
+        <v/>
+      </c>
+      <c r="M453" t="str">
+        <v/>
+      </c>
+      <c r="N453" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O453" t="str">
+        <v/>
+      </c>
+      <c r="P453" t="str">
+        <v/>
+      </c>
+      <c r="Q453" t="str">
+        <v/>
+      </c>
+      <c r="R453" t="str">
+        <v/>
+      </c>
+      <c r="S453" t="str">
+        <v/>
+      </c>
+      <c r="T453" t="str">
+        <v/>
+      </c>
+      <c r="U453" t="str">
+        <v/>
+      </c>
+      <c r="V453" t="str">
+        <v/>
+      </c>
+      <c r="W453" t="str">
+        <v/>
+      </c>
+      <c r="X453" t="str">
+        <v/>
+      </c>
+      <c r="Y453" t="str">
+        <v/>
+      </c>
+      <c r="Z453" t="str">
+        <v/>
+      </c>
+      <c r="AA453" t="str">
+        <v/>
+      </c>
+      <c r="AB453" t="str">
+        <v>email: Fw: Claire Wince (CONFIRMED) Booking No: HE36SJ 16/12/2026 DMK ✈ HKT</v>
+      </c>
+      <c r="AC453" t="str">
+        <v/>
+      </c>
+      <c r="AD453" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE453" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="str">
+        <v>2027-06-04</v>
+      </c>
+      <c r="B454" t="str">
+        <v>Friday</v>
+      </c>
+      <c r="C454" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D454" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E454" t="str">
+        <v/>
+      </c>
+      <c r="F454" t="str">
+        <v/>
+      </c>
+      <c r="G454" t="str">
+        <v/>
+      </c>
+      <c r="H454" t="str">
+        <v/>
+      </c>
+      <c r="I454" t="str">
+        <v/>
+      </c>
+      <c r="J454" t="str">
+        <v/>
+      </c>
+      <c r="K454" t="str">
+        <v/>
+      </c>
+      <c r="L454" t="str">
+        <v/>
+      </c>
+      <c r="M454" t="str">
+        <v/>
+      </c>
+      <c r="N454" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O454" t="str">
+        <v/>
+      </c>
+      <c r="P454" t="str">
+        <v/>
+      </c>
+      <c r="Q454" t="str">
+        <v/>
+      </c>
+      <c r="R454" t="str">
+        <v/>
+      </c>
+      <c r="S454" t="str">
+        <v/>
+      </c>
+      <c r="T454" t="str">
+        <v/>
+      </c>
+      <c r="U454" t="str">
+        <v/>
+      </c>
+      <c r="V454" t="str">
+        <v/>
+      </c>
+      <c r="W454" t="str">
+        <v/>
+      </c>
+      <c r="X454" t="str">
+        <v/>
+      </c>
+      <c r="Y454" t="str">
+        <v/>
+      </c>
+      <c r="Z454" t="str">
+        <v/>
+      </c>
+      <c r="AA454" t="str">
+        <v/>
+      </c>
+      <c r="AB454" t="str">
         <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
       </c>
-      <c r="AC447" t="str">
-        <v/>
-      </c>
-      <c r="AD447" t="str">
-        <v>Yes</v>
-      </c>
-      <c r="AE447" t="str">
+      <c r="AC454" t="str">
+        <v/>
+      </c>
+      <c r="AD454" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE454" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="str">
+        <v>2027-06-05</v>
+      </c>
+      <c r="B455" t="str">
+        <v>Saturday</v>
+      </c>
+      <c r="C455" t="str">
+        <v>, Madrid</v>
+      </c>
+      <c r="D455" t="str">
+        <v>Steve Brazier</v>
+      </c>
+      <c r="E455" t="str">
+        <v/>
+      </c>
+      <c r="F455" t="str">
+        <v/>
+      </c>
+      <c r="G455" t="str">
+        <v/>
+      </c>
+      <c r="H455" t="str">
+        <v/>
+      </c>
+      <c r="I455" t="str">
+        <v/>
+      </c>
+      <c r="J455" t="str">
+        <v/>
+      </c>
+      <c r="K455" t="str">
+        <v/>
+      </c>
+      <c r="L455" t="str">
+        <v/>
+      </c>
+      <c r="M455" t="str">
+        <v/>
+      </c>
+      <c r="N455" t="str">
+        <v>Booking</v>
+      </c>
+      <c r="O455" t="str">
+        <v/>
+      </c>
+      <c r="P455" t="str">
+        <v/>
+      </c>
+      <c r="Q455" t="str">
+        <v/>
+      </c>
+      <c r="R455" t="str">
+        <v/>
+      </c>
+      <c r="S455" t="str">
+        <v/>
+      </c>
+      <c r="T455" t="str">
+        <v/>
+      </c>
+      <c r="U455" t="str">
+        <v/>
+      </c>
+      <c r="V455" t="str">
+        <v/>
+      </c>
+      <c r="W455" t="str">
+        <v/>
+      </c>
+      <c r="X455" t="str">
+        <v/>
+      </c>
+      <c r="Y455" t="str">
+        <v/>
+      </c>
+      <c r="Z455" t="str">
+        <v/>
+      </c>
+      <c r="AA455" t="str">
+        <v/>
+      </c>
+      <c r="AB455" t="str">
+        <v>email: Reservation Confirmation #82680619 for The Palace, a Luxury Collection Hotel, Madrid</v>
+      </c>
+      <c r="AC455" t="str">
+        <v/>
+      </c>
+      <c r="AD455" t="str">
+        <v>Yes</v>
+      </c>
+      <c r="AE455" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE447"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE455"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -42919,18 +43679,18 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>UK</v>
+        <v>Italy</v>
       </c>
       <c r="B2">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Italy</v>
+        <v>UK</v>
       </c>
       <c r="B3">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="4">
@@ -43074,7 +43834,7 @@
         <v>UK nights (max 90)</v>
       </c>
       <c r="B22">
-        <v>120</v>
+        <v>123</v>
       </c>
     </row>
     <row r="23">
@@ -43082,7 +43842,7 @@
         <v>Italy days (target 183+)</v>
       </c>
       <c r="B23">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="24">
@@ -43122,7 +43882,7 @@
         <v>Total entries</v>
       </c>
       <c r="B28">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="30">
@@ -43130,7 +43890,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-26</v>
+        <v>2026-10-27</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -42154,7 +42154,7 @@
         <v/>
       </c>
       <c r="G440" t="str">
-        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0</v>
+        <v>Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-25 12:04:47 GMT+0</v>
       </c>
       <c r="H440" t="str">
         <v>45.8436503</v>
@@ -42249,7 +42249,7 @@
         <v/>
       </c>
       <c r="G441" t="str">
-        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0</v>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0 | Inferred from evening bracket at known location: Cernobbio 2026-10-26 19:57:13 GMT+0</v>
       </c>
       <c r="H441" t="str">
         <v>45.8436497</v>
@@ -42332,10 +42332,10 @@
         <v>Tuesday</v>
       </c>
       <c r="C442" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D442" t="str">
-        <v>Milan</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E442" t="str">
         <v>Italy</v>
@@ -42344,19 +42344,19 @@
         <v/>
       </c>
       <c r="G442" t="str">
-        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT</v>
       </c>
       <c r="H442" t="str">
-        <v/>
+        <v>45.8436505</v>
       </c>
       <c r="I442" t="str">
-        <v/>
+        <v>9.0666602</v>
       </c>
       <c r="J442" t="str">
-        <v/>
+        <v>2026-10-27 15:15:45 GMT</v>
       </c>
       <c r="K442" t="str">
-        <v/>
+        <v>bracket-inference</v>
       </c>
       <c r="L442" t="str">
         <v/>
@@ -42365,43 +42365,43 @@
         <v/>
       </c>
       <c r="N442" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O442" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P442" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q442" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R442" t="str">
-        <v/>
+        <v>2026-10-27 15:15:45 GMT</v>
       </c>
       <c r="S442" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="T442" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="U442" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="V442" t="str">
-        <v/>
+        <v>2026-10-28 03:36:23 GMT</v>
       </c>
       <c r="W442" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X442" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y442" t="str">
-        <v/>
+        <v>15:15 UK/16:15 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z442" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA442" t="str">
         <v/>
@@ -42410,7 +42410,7 @@
         <v>flight-inference: BA584→BA581</v>
       </c>
       <c r="AC442" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD442" t="str">
         <v>Yes</v>
@@ -42427,10 +42427,10 @@
         <v>Wednesday</v>
       </c>
       <c r="C443" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="D443" t="str">
-        <v>Milan</v>
+        <v>Cernobbio</v>
       </c>
       <c r="E443" t="str">
         <v>Italy</v>
@@ -42439,19 +42439,19 @@
         <v/>
       </c>
       <c r="G443" t="str">
-        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT</v>
       </c>
       <c r="H443" t="str">
-        <v/>
+        <v>45.8436506</v>
       </c>
       <c r="I443" t="str">
-        <v/>
+        <v>9.0666565</v>
       </c>
       <c r="J443" t="str">
-        <v/>
+        <v>2026-10-28 06:49:08 GMT</v>
       </c>
       <c r="K443" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L443" t="str">
         <v/>
@@ -42460,19 +42460,19 @@
         <v/>
       </c>
       <c r="N443" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O443" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P443" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q443" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R443" t="str">
-        <v/>
+        <v>2026-10-28 06:49:08 GMT</v>
       </c>
       <c r="S443" t="str">
         <v/>
@@ -42487,16 +42487,16 @@
         <v/>
       </c>
       <c r="W443" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X443" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y443" t="str">
-        <v/>
+        <v>03:36 UK/04:36 Europe/Rome Cernobbio, Italy | 06:49 UK/07:49 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z443" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA443" t="str">
         <v/>
@@ -42505,7 +42505,7 @@
         <v>flight-inference: BA584→BA581</v>
       </c>
       <c r="AC443" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD443" t="str">
         <v>Yes</v>
@@ -43890,7 +43890,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-27</v>
+        <v>2026-10-28</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -43890,7 +43890,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-28</v>
+        <v>2026-10-29</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -42344,7 +42344,7 @@
         <v/>
       </c>
       <c r="G442" t="str">
-        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT</v>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-27 15:15:45 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT | Inferred from GPS brackets: evening=Cernobbio 2026-10-27 15:15:45 GMT, morning=Cernobbio 2026-10-28 03:36:23 GMT</v>
       </c>
       <c r="H442" t="str">
         <v>45.8436505</v>
@@ -42439,7 +42439,7 @@
         <v/>
       </c>
       <c r="G443" t="str">
-        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT</v>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT</v>
       </c>
       <c r="H443" t="str">
         <v>45.8436506</v>
@@ -42558,16 +42558,16 @@
         <v>Booking</v>
       </c>
       <c r="O444" t="str">
-        <v/>
+        <v>Cernobbio</v>
       </c>
       <c r="P444" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q444" t="str">
-        <v/>
+        <v>45.84365, 9.06666</v>
       </c>
       <c r="R444" t="str">
-        <v/>
+        <v>2026-10-29 21:08:31 GMT</v>
       </c>
       <c r="S444" t="str">
         <v/>
@@ -42585,13 +42585,13 @@
         <v/>
       </c>
       <c r="X444" t="str">
-        <v/>
+        <v>2</v>
       </c>
       <c r="Y444" t="str">
-        <v/>
+        <v>15:33 UK/16:33 Europe/Rome Cernobbio, Italy | 21:08 UK/22:08 Europe/Rome Cernobbio, Italy</v>
       </c>
       <c r="Z444" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AA444" t="str">
         <v/>
@@ -43890,7 +43890,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-29</v>
+        <v>2026-10-30</v>
       </c>
     </row>
   </sheetData>

--- a/backups/latest.xlsx
+++ b/backups/latest.xlsx
@@ -42439,7 +42439,7 @@
         <v/>
       </c>
       <c r="G443" t="str">
-        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT</v>
+        <v>Flight-inferred country Italy from BA584→BA581 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 03:36:23 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT | Inferred from evening bracket at known location: Cernobbio 2026-10-28 06:49:08 GMT</v>
       </c>
       <c r="H443" t="str">
         <v>45.8436506</v>
@@ -42617,10 +42617,10 @@
         <v>Friday</v>
       </c>
       <c r="C445" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="D445" t="str">
-        <v>London</v>
+        <v>Oxford</v>
       </c>
       <c r="E445" t="str">
         <v>UK</v>
@@ -42632,10 +42632,10 @@
         <v/>
       </c>
       <c r="H445" t="str">
-        <v/>
+        <v>51.733026</v>
       </c>
       <c r="I445" t="str">
-        <v/>
+        <v>-1.2371727</v>
       </c>
       <c r="J445" t="str">
         <v/>
@@ -42653,43 +42653,43 @@
         <v>Booking</v>
       </c>
       <c r="O445" t="str">
-        <v/>
+        <v>Ferno</v>
       </c>
       <c r="P445" t="str">
-        <v/>
+        <v>Italy</v>
       </c>
       <c r="Q445" t="str">
-        <v/>
+        <v>45.62715, 8.71529</v>
       </c>
       <c r="R445" t="str">
-        <v/>
+        <v>2026-10-30 11:29:38 GMT</v>
       </c>
       <c r="S445" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="T445" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="U445" t="str">
-        <v/>
+        <v>51.73303, -1.23717</v>
       </c>
       <c r="V445" t="str">
-        <v/>
+        <v>2026-10-31 06:23:19 GMT</v>
       </c>
       <c r="W445" t="str">
         <v/>
       </c>
       <c r="X445" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y445" t="str">
-        <v/>
+        <v>11:29 UK/12:29 Europe/Rome Ferno, Italy</v>
       </c>
       <c r="Z445" t="str">
         <v/>
       </c>
       <c r="AA445" t="str">
-        <v/>
+        <v>Flight says UK; GPS brackets differ (ev=Italy, am=UK) — kept flight country, please confirm</v>
       </c>
       <c r="AB445" t="str">
         <v>calendar+email: Flight BA581: MXP - LHR, departs 12:45 | Fw: Your booking confirmation ZRDGS4</v>
@@ -42712,10 +42712,10 @@
         <v>Saturday</v>
       </c>
       <c r="C446" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="D446" t="str">
-        <v>London</v>
+        <v>Oxford</v>
       </c>
       <c r="E446" t="str">
         <v>UK</v>
@@ -42724,19 +42724,19 @@
         <v/>
       </c>
       <c r="G446" t="str">
-        <v>Flight-inferred country UK from BA581→BA588 stay — night between arrival and return flight (UK midnight rule).</v>
+        <v>Flight-inferred country UK from BA581→BA588 stay — night between arrival and return flight (UK midnight rule). | Inferred from evening bracket at known location: Oxford 2026-10-31 06:23:19 GMT | Inferred from evening bracket at known location: Oxford 2026-10-31 06:23:19 GMT</v>
       </c>
       <c r="H446" t="str">
-        <v/>
+        <v>51.733026</v>
       </c>
       <c r="I446" t="str">
-        <v/>
+        <v>-1.2371727</v>
       </c>
       <c r="J446" t="str">
-        <v/>
+        <v>2026-10-31 06:23:19 GMT</v>
       </c>
       <c r="K446" t="str">
-        <v/>
+        <v>single-bracket-inference</v>
       </c>
       <c r="L446" t="str">
         <v/>
@@ -42745,19 +42745,19 @@
         <v/>
       </c>
       <c r="N446" t="str">
-        <v>Booking</v>
+        <v>Bracket GPS</v>
       </c>
       <c r="O446" t="str">
-        <v/>
+        <v>Oxford</v>
       </c>
       <c r="P446" t="str">
-        <v/>
+        <v>UK</v>
       </c>
       <c r="Q446" t="str">
-        <v/>
+        <v>51.73303, -1.23717</v>
       </c>
       <c r="R446" t="str">
-        <v/>
+        <v>2026-10-31 06:23:19 GMT</v>
       </c>
       <c r="S446" t="str">
         <v/>
@@ -42772,13 +42772,13 @@
         <v/>
       </c>
       <c r="W446" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="X446" t="str">
-        <v/>
+        <v>1</v>
       </c>
       <c r="Y446" t="str">
-        <v/>
+        <v>06:23 UK Oxford, UK</v>
       </c>
       <c r="Z446" t="str">
         <v/>
@@ -42790,7 +42790,7 @@
         <v>email: Fw: Your booking confirmation ZRDGS4</v>
       </c>
       <c r="AC446" t="str">
-        <v/>
+        <v>Yes</v>
       </c>
       <c r="AD446" t="str">
         <v>Yes</v>
@@ -43890,7 +43890,7 @@
         <v>Backup date</v>
       </c>
       <c r="B30" t="str">
-        <v>2026-10-30</v>
+        <v>2026-10-31</v>
       </c>
     </row>
   </sheetData>
